--- a/data/output/sim_gridrnd/ABS1/group_500_60/results/ABS1_G6_results_summary.xlsx
+++ b/data/output/sim_gridrnd/ABS1/group_500_60/results/ABS1_G6_results_summary.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Results" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB23"/>
+  <dimension ref="A1:CM23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,24 +436,24 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>mu</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>sigma</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>jnd</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>pse</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>jnd</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>sigma</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>mu</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>n_trials</t>
@@ -466,367 +466,422 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>lat_entropy_100</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_120</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_140</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_160</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_180</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_200</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_40</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_60</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_80</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>model</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>pse_40</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>jnd_40</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>pse_60</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>jnd_60</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>pse_80</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>jnd_80</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>pse_100</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>jnd_100</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>pse_120</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>jnd_120</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>pse_140</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>jnd_140</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>pse_160</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>jnd_160</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>pse_180</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>jnd_180</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>pse_200</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>jnd_200</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_40</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_60</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_80</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_100</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_120</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_140</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_160</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_180</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_200</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_40</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_60</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_80</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_100</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_120</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_140</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_160</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_180</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_200</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_40</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_60</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_80</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_100</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_120</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_140</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_160</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_180</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_200</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_40</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_60</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_80</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_100</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_120</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_140</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_160</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_180</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_200</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_40</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_60</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_80</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_100</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_120</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_140</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_160</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_180</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_200</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_40</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_60</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_80</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_100</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_120</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_140</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_160</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_180</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_200</t>
+        </is>
+      </c>
+      <c r="CL1" s="1" t="inlineStr">
+        <is>
+          <t>pse_est</t>
+        </is>
+      </c>
+      <c r="CM1" s="1" t="inlineStr">
+        <is>
+          <t>jnd_est</t>
         </is>
       </c>
     </row>
@@ -840,10 +895,10 @@
         <v>502</v>
       </c>
       <c r="C2" t="n">
+        <v>85.9896219421794</v>
+      </c>
+      <c r="D2" t="n">
         <v>58</v>
-      </c>
-      <c r="D2" t="n">
-        <v>85.9896219421794</v>
       </c>
       <c r="E2" t="n">
         <v>502</v>
@@ -852,720 +907,819 @@
         <v>200</v>
       </c>
       <c r="G2" t="n">
-        <v>0.495</v>
-      </c>
-      <c r="H2" t="inlineStr">
+        <v>78</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="K2" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="L2" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="M2" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="O2" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="Q2" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I2" t="n">
-        <v>499.7003343187643</v>
-      </c>
-      <c r="J2" t="n">
-        <v>70.99908893749789</v>
-      </c>
-      <c r="K2" t="n">
-        <v>503.1310632266749</v>
-      </c>
-      <c r="L2" t="n">
-        <v>61.71430665361473</v>
-      </c>
-      <c r="M2" t="n">
-        <v>514.0338668390767</v>
-      </c>
-      <c r="N2" t="n">
-        <v>86.63341824177122</v>
-      </c>
-      <c r="O2" t="n">
-        <v>509.1161098173413</v>
-      </c>
-      <c r="P2" t="n">
-        <v>88.20785522443042</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>506.5656235128841</v>
-      </c>
       <c r="R2" t="n">
-        <v>90.44689188104013</v>
+        <v>499.7</v>
       </c>
       <c r="S2" t="n">
-        <v>511.0077366561225</v>
+        <v>71</v>
       </c>
       <c r="T2" t="n">
-        <v>90.03750175028105</v>
+        <v>503.13</v>
       </c>
       <c r="U2" t="n">
-        <v>507.099508497617</v>
+        <v>61.71</v>
       </c>
       <c r="V2" t="n">
-        <v>83.53494468572178</v>
+        <v>514.03</v>
       </c>
       <c r="W2" t="n">
-        <v>503.8428749745448</v>
+        <v>86.63</v>
       </c>
       <c r="X2" t="n">
-        <v>81.83402502675881</v>
+        <v>509.12</v>
       </c>
       <c r="Y2" t="n">
-        <v>505.4037109554533</v>
+        <v>88.20999999999999</v>
       </c>
       <c r="Z2" t="n">
-        <v>77.99093237051277</v>
+        <v>506.57</v>
       </c>
       <c r="AA2" t="n">
+        <v>90.45</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>511.01</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>90.04000000000001</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>507.1</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>83.53</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>503.84</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>81.83</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>505.4</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>77.98999999999999</v>
+      </c>
+      <c r="AJ2" t="n">
         <v>0</v>
       </c>
-      <c r="AB2" t="n">
+      <c r="AK2" t="n">
         <v>0</v>
       </c>
-      <c r="AC2" t="n">
+      <c r="AL2" t="n">
         <v>0.125</v>
       </c>
-      <c r="AD2" t="n">
+      <c r="AM2" t="n">
         <v>0.06</v>
       </c>
-      <c r="AE2" t="n">
+      <c r="AN2" t="n">
         <v>0.03333333333333333</v>
       </c>
-      <c r="AF2" t="n">
+      <c r="AO2" t="n">
         <v>0.04285714285714286</v>
       </c>
-      <c r="AG2" t="n">
+      <c r="AP2" t="n">
         <v>0.025</v>
       </c>
-      <c r="AH2" t="n">
+      <c r="AQ2" t="n">
         <v>0.01111111111111111</v>
       </c>
-      <c r="AI2" t="n">
+      <c r="AR2" t="n">
         <v>0.01</v>
       </c>
-      <c r="AJ2" t="n">
+      <c r="AS2" t="n">
         <v>491.675</v>
       </c>
-      <c r="AK2" t="n">
+      <c r="AT2" t="n">
         <v>493.1833333333333</v>
       </c>
-      <c r="AL2" t="n">
+      <c r="AU2" t="n">
         <v>508.6625</v>
       </c>
-      <c r="AM2" t="n">
+      <c r="AV2" t="n">
         <v>505.22</v>
       </c>
-      <c r="AN2" t="n">
+      <c r="AW2" t="n">
         <v>503.4833333333333</v>
       </c>
-      <c r="AO2" t="n">
+      <c r="AX2" t="n">
         <v>505.5285714285714</v>
       </c>
-      <c r="AP2" t="n">
+      <c r="AY2" t="n">
         <v>504.925</v>
       </c>
-      <c r="AQ2" t="n">
+      <c r="AZ2" t="n">
         <v>504.1611111111111</v>
       </c>
-      <c r="AR2" t="n">
+      <c r="BA2" t="n">
         <v>503.96</v>
       </c>
-      <c r="AS2" t="n">
+      <c r="BB2" t="n">
         <v>62.48415299097844</v>
       </c>
-      <c r="AT2" t="n">
+      <c r="BC2" t="n">
         <v>65.35989893573039</v>
       </c>
-      <c r="AU2" t="n">
+      <c r="BD2" t="n">
         <v>70.90326927406097</v>
       </c>
-      <c r="AV2" t="n">
+      <c r="BE2" t="n">
         <v>75.12703641166739</v>
       </c>
-      <c r="AW2" t="n">
+      <c r="BF2" t="n">
         <v>77.47332695120875</v>
       </c>
-      <c r="AX2" t="n">
+      <c r="BG2" t="n">
         <v>79.77311065561797</v>
       </c>
-      <c r="AY2" t="n">
+      <c r="BH2" t="n">
         <v>81.08603070196494</v>
       </c>
-      <c r="AZ2" t="n">
+      <c r="BI2" t="n">
         <v>80.45600342829813</v>
       </c>
-      <c r="BA2" t="n">
+      <c r="BJ2" t="n">
         <v>79.96216855488601</v>
       </c>
-      <c r="BB2" t="n">
+      <c r="BK2" t="n">
         <v>353</v>
       </c>
-      <c r="BC2" t="n">
+      <c r="BL2" t="n">
         <v>353</v>
       </c>
-      <c r="BD2" t="n">
+      <c r="BM2" t="n">
         <v>353</v>
       </c>
-      <c r="BE2" t="n">
+      <c r="BN2" t="n">
         <v>353</v>
       </c>
-      <c r="BF2" t="n">
+      <c r="BO2" t="n">
         <v>353</v>
       </c>
-      <c r="BG2" t="n">
+      <c r="BP2" t="n">
         <v>353</v>
       </c>
-      <c r="BH2" t="n">
+      <c r="BQ2" t="n">
         <v>353</v>
       </c>
-      <c r="BI2" t="n">
+      <c r="BR2" t="n">
         <v>353</v>
       </c>
-      <c r="BJ2" t="n">
+      <c r="BS2" t="n">
         <v>353</v>
       </c>
-      <c r="BK2" t="n">
+      <c r="BT2" t="n">
         <v>578</v>
       </c>
-      <c r="BL2" t="n">
+      <c r="BU2" t="n">
         <v>589</v>
       </c>
-      <c r="BM2" t="n">
+      <c r="BV2" t="n">
         <v>619</v>
       </c>
-      <c r="BN2" t="n">
+      <c r="BW2" t="n">
         <v>619</v>
       </c>
-      <c r="BO2" t="n">
+      <c r="BX2" t="n">
         <v>619</v>
       </c>
-      <c r="BP2" t="n">
+      <c r="BY2" t="n">
         <v>619</v>
       </c>
-      <c r="BQ2" t="n">
+      <c r="BZ2" t="n">
         <v>619</v>
       </c>
-      <c r="BR2" t="n">
+      <c r="CA2" t="n">
         <v>619</v>
       </c>
-      <c r="BS2" t="n">
+      <c r="CB2" t="n">
         <v>619</v>
       </c>
-      <c r="BT2" t="n">
+      <c r="CC2" t="n">
         <v>0.8333333333333334</v>
       </c>
-      <c r="BU2" t="n">
+      <c r="CD2" t="n">
         <v>0.2727272727272727</v>
       </c>
-      <c r="BV2" t="n">
+      <c r="CE2" t="n">
         <v>0.9285714285714286</v>
       </c>
-      <c r="BW2" t="n">
+      <c r="CF2" t="n">
         <v>0.7647058823529411</v>
       </c>
-      <c r="BX2" t="n">
+      <c r="CG2" t="n">
         <v>0.6363636363636364</v>
       </c>
-      <c r="BY2" t="n">
+      <c r="CH2" t="n">
         <v>0.7916666666666666</v>
       </c>
-      <c r="BZ2" t="n">
+      <c r="CI2" t="n">
         <v>0.8928571428571429</v>
       </c>
-      <c r="CA2" t="n">
+      <c r="CJ2" t="n">
         <v>0.8333333333333334</v>
       </c>
-      <c r="CB2" t="n">
+      <c r="CK2" t="n">
         <v>0.7878787878787878</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>505.4</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>77.98999999999999</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S03_G6_502_59_ABS1</t>
+          <t>S02_G6_498_60_ABS1</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="C3" t="n">
-        <v>59</v>
+        <v>88.95478131949592</v>
       </c>
       <c r="D3" t="n">
-        <v>87.47220163083766</v>
+        <v>60</v>
       </c>
       <c r="E3" t="n">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="F3" t="n">
         <v>200</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H3" t="inlineStr">
+        <v>76.5</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="J3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="M3" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="N3" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="O3" t="n">
+        <v>3</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I3" t="n">
-        <v>530.8875468607673</v>
-      </c>
-      <c r="J3" t="n">
-        <v>44.91808549061582</v>
-      </c>
-      <c r="K3" t="n">
-        <v>524.2884346578904</v>
-      </c>
-      <c r="L3" t="n">
-        <v>51.94612605371309</v>
-      </c>
-      <c r="M3" t="n">
-        <v>518.7145065445427</v>
-      </c>
-      <c r="N3" t="n">
-        <v>47.23455310966894</v>
-      </c>
-      <c r="O3" t="n">
-        <v>516.6726215054534</v>
-      </c>
-      <c r="P3" t="n">
-        <v>56.83640559979581</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>520.9498824867443</v>
-      </c>
       <c r="R3" t="n">
-        <v>69.4477248859716</v>
+        <v>514.74</v>
       </c>
       <c r="S3" t="n">
-        <v>518.1176343570029</v>
+        <v>55.56</v>
       </c>
       <c r="T3" t="n">
-        <v>64.10253846771096</v>
+        <v>510.78</v>
       </c>
       <c r="U3" t="n">
-        <v>514.1852169897841</v>
+        <v>48.43</v>
       </c>
       <c r="V3" t="n">
-        <v>68.45305966726538</v>
+        <v>512.02</v>
       </c>
       <c r="W3" t="n">
-        <v>513.1318269931293</v>
+        <v>59.42</v>
       </c>
       <c r="X3" t="n">
-        <v>76.6718879835183</v>
+        <v>511.78</v>
       </c>
       <c r="Y3" t="n">
-        <v>515.8318325760835</v>
+        <v>52.86</v>
       </c>
       <c r="Z3" t="n">
-        <v>76.93458214831715</v>
+        <v>517.15</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.4871794871794872</v>
+        <v>54.44</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.288135593220339</v>
+        <v>519.25</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.1392405063291139</v>
+        <v>54.76</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.1111111111111111</v>
+        <v>515.6900000000001</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.1428571428571428</v>
+        <v>56.57</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.09352517985611511</v>
+        <v>513.73</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.0440251572327044</v>
+        <v>56.72</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.02793296089385475</v>
+        <v>512.5</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.03517587939698492</v>
+        <v>54.99</v>
       </c>
       <c r="AJ3" t="n">
-        <v>524.6</v>
+        <v>0.1</v>
       </c>
       <c r="AK3" t="n">
-        <v>523.5</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="AL3" t="n">
-        <v>519.0125</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>519.13</v>
+        <v>0.02</v>
       </c>
       <c r="AN3" t="n">
-        <v>522.775</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="AO3" t="n">
-        <v>519.8142857142857</v>
+        <v>0.02857142857142857</v>
       </c>
       <c r="AP3" t="n">
-        <v>516.125</v>
+        <v>0.025</v>
       </c>
       <c r="AQ3" t="n">
-        <v>515.0333333333333</v>
+        <v>0.01111111111111111</v>
       </c>
       <c r="AR3" t="n">
-        <v>515.91</v>
+        <v>0.01</v>
       </c>
       <c r="AS3" t="n">
-        <v>48.19273804215734</v>
+        <v>515.15</v>
       </c>
       <c r="AT3" t="n">
-        <v>52.97373563065631</v>
+        <v>515.2</v>
       </c>
       <c r="AU3" t="n">
-        <v>53.25516260185486</v>
+        <v>512.6375</v>
       </c>
       <c r="AV3" t="n">
-        <v>54.74205969818819</v>
+        <v>514.51</v>
       </c>
       <c r="AW3" t="n">
-        <v>57.32908838451907</v>
+        <v>515.0166666666667</v>
       </c>
       <c r="AX3" t="n">
-        <v>60.84671439824194</v>
+        <v>515.6785714285714</v>
       </c>
       <c r="AY3" t="n">
-        <v>63.02705272341394</v>
+        <v>515.625</v>
       </c>
       <c r="AZ3" t="n">
-        <v>65.54929442793416</v>
+        <v>515.2166666666667</v>
       </c>
       <c r="BA3" t="n">
-        <v>67.77840290239952</v>
+        <v>515.09</v>
       </c>
       <c r="BB3" t="n">
-        <v>358</v>
+        <v>51.75449255861756</v>
       </c>
       <c r="BC3" t="n">
-        <v>358</v>
+        <v>52.7325958650498</v>
       </c>
       <c r="BD3" t="n">
-        <v>358</v>
+        <v>56.46464463493948</v>
       </c>
       <c r="BE3" t="n">
-        <v>358</v>
+        <v>57.0418258824172</v>
       </c>
       <c r="BF3" t="n">
-        <v>358</v>
+        <v>56.79685779649747</v>
       </c>
       <c r="BG3" t="n">
-        <v>358</v>
+        <v>56.23144365123521</v>
       </c>
       <c r="BH3" t="n">
-        <v>358</v>
+        <v>56.06054205053676</v>
       </c>
       <c r="BI3" t="n">
-        <v>358</v>
+        <v>55.99794391066713</v>
       </c>
       <c r="BJ3" t="n">
-        <v>358</v>
+        <v>55.78926330397275</v>
       </c>
       <c r="BK3" t="n">
-        <v>643</v>
+        <v>429</v>
       </c>
       <c r="BL3" t="n">
-        <v>643</v>
+        <v>429</v>
       </c>
       <c r="BM3" t="n">
-        <v>643</v>
+        <v>427</v>
       </c>
       <c r="BN3" t="n">
-        <v>643</v>
+        <v>427</v>
       </c>
       <c r="BO3" t="n">
-        <v>643</v>
+        <v>427</v>
       </c>
       <c r="BP3" t="n">
-        <v>643</v>
+        <v>427</v>
       </c>
       <c r="BQ3" t="n">
-        <v>643</v>
+        <v>427</v>
       </c>
       <c r="BR3" t="n">
-        <v>643</v>
+        <v>427</v>
       </c>
       <c r="BS3" t="n">
-        <v>643</v>
+        <v>427</v>
       </c>
       <c r="BT3" t="n">
-        <v>0.3636363636363636</v>
+        <v>635</v>
       </c>
       <c r="BU3" t="n">
+        <v>635</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>635</v>
+      </c>
+      <c r="BW3" t="n">
+        <v>635</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>635</v>
+      </c>
+      <c r="BY3" t="n">
+        <v>635</v>
+      </c>
+      <c r="BZ3" t="n">
+        <v>635</v>
+      </c>
+      <c r="CA3" t="n">
+        <v>635</v>
+      </c>
+      <c r="CB3" t="n">
+        <v>635</v>
+      </c>
+      <c r="CC3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="CD3" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="CE3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="CF3" t="n">
         <v>1</v>
       </c>
-      <c r="BV3" t="n">
-        <v>0.6470588235294118</v>
-      </c>
-      <c r="BW3" t="n">
-        <v>0.6111111111111112</v>
-      </c>
-      <c r="BX3" t="n">
+      <c r="CG3" t="n">
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="CH3" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="CI3" t="n">
+        <v>0.9130434782608695</v>
+      </c>
+      <c r="CJ3" t="n">
         <v>1</v>
       </c>
-      <c r="BY3" t="n">
-        <v>0.8260869565217391</v>
-      </c>
-      <c r="BZ3" t="n">
-        <v>0.8076923076923077</v>
-      </c>
-      <c r="CA3" t="n">
-        <v>0.71875</v>
-      </c>
-      <c r="CB3" t="n">
-        <v>0.75</v>
+      <c r="CK3" t="n">
+        <v>0.9666666666666667</v>
+      </c>
+      <c r="CL3" t="n">
+        <v>512.5</v>
+      </c>
+      <c r="CM3" t="n">
+        <v>54.99</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S02_G6_498_60_ABS1</t>
+          <t>S03_G6_502_59_ABS1</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="C4" t="n">
-        <v>60</v>
+        <v>87.47220163083766</v>
       </c>
       <c r="D4" t="n">
-        <v>88.95478131949592</v>
+        <v>59</v>
       </c>
       <c r="E4" t="n">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="F4" t="n">
         <v>200</v>
       </c>
       <c r="G4" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="H4" t="inlineStr">
+        <v>73.5</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="L4" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="M4" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="Q4" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I4" t="n">
-        <v>514.7416035129296</v>
-      </c>
-      <c r="J4" t="n">
-        <v>55.55846170970973</v>
-      </c>
-      <c r="K4" t="n">
-        <v>510.7784665140879</v>
-      </c>
-      <c r="L4" t="n">
-        <v>48.42594982779598</v>
-      </c>
-      <c r="M4" t="n">
-        <v>512.0175933930926</v>
-      </c>
-      <c r="N4" t="n">
-        <v>59.4153151103794</v>
-      </c>
-      <c r="O4" t="n">
-        <v>511.779886524031</v>
-      </c>
-      <c r="P4" t="n">
-        <v>52.86193703040898</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>517.150591144336</v>
-      </c>
       <c r="R4" t="n">
-        <v>54.43816526673052</v>
+        <v>530.89</v>
       </c>
       <c r="S4" t="n">
-        <v>519.2470009185328</v>
+        <v>44.92</v>
       </c>
       <c r="T4" t="n">
-        <v>54.75701055181714</v>
+        <v>524.29</v>
       </c>
       <c r="U4" t="n">
-        <v>515.6883855562868</v>
+        <v>51.95</v>
       </c>
       <c r="V4" t="n">
-        <v>56.56674766093045</v>
+        <v>518.71</v>
       </c>
       <c r="W4" t="n">
-        <v>513.7276307565063</v>
+        <v>47.23</v>
       </c>
       <c r="X4" t="n">
-        <v>56.72313949039758</v>
+        <v>516.67</v>
       </c>
       <c r="Y4" t="n">
-        <v>512.5019460016634</v>
+        <v>56.84</v>
       </c>
       <c r="Z4" t="n">
-        <v>54.99233226710277</v>
+        <v>520.95</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.1</v>
+        <v>69.45</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.03333333333333333</v>
+        <v>518.12</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.02</v>
+        <v>514.1900000000001</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.03333333333333333</v>
+        <v>68.45</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.02857142857142857</v>
+        <v>513.13</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.025</v>
+        <v>76.67</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.01111111111111111</v>
+        <v>515.83</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.01</v>
+        <v>76.93000000000001</v>
       </c>
       <c r="AJ4" t="n">
-        <v>515.15</v>
+        <v>0.4871794871794872</v>
       </c>
       <c r="AK4" t="n">
-        <v>515.2</v>
+        <v>0.288135593220339</v>
       </c>
       <c r="AL4" t="n">
-        <v>512.6375</v>
+        <v>0.1392405063291139</v>
       </c>
       <c r="AM4" t="n">
-        <v>514.51</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="AN4" t="n">
-        <v>515.0166666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AO4" t="n">
-        <v>515.6785714285714</v>
+        <v>0.09352517985611511</v>
       </c>
       <c r="AP4" t="n">
-        <v>515.625</v>
+        <v>0.0440251572327044</v>
       </c>
       <c r="AQ4" t="n">
-        <v>515.2166666666667</v>
+        <v>0.02793296089385475</v>
       </c>
       <c r="AR4" t="n">
-        <v>515.09</v>
+        <v>0.03517587939698492</v>
       </c>
       <c r="AS4" t="n">
-        <v>51.75449255861756</v>
+        <v>524.6</v>
       </c>
       <c r="AT4" t="n">
-        <v>52.7325958650498</v>
+        <v>523.5</v>
       </c>
       <c r="AU4" t="n">
-        <v>56.46464463493948</v>
+        <v>519.0125</v>
       </c>
       <c r="AV4" t="n">
-        <v>57.0418258824172</v>
+        <v>519.13</v>
       </c>
       <c r="AW4" t="n">
-        <v>56.79685779649747</v>
+        <v>522.775</v>
       </c>
       <c r="AX4" t="n">
-        <v>56.23144365123521</v>
+        <v>519.8142857142857</v>
       </c>
       <c r="AY4" t="n">
-        <v>56.06054205053676</v>
+        <v>516.125</v>
       </c>
       <c r="AZ4" t="n">
-        <v>55.99794391066713</v>
+        <v>515.0333333333333</v>
       </c>
       <c r="BA4" t="n">
-        <v>55.78926330397275</v>
+        <v>515.91</v>
       </c>
       <c r="BB4" t="n">
-        <v>429</v>
+        <v>48.19273804215734</v>
       </c>
       <c r="BC4" t="n">
-        <v>429</v>
+        <v>52.97373563065631</v>
       </c>
       <c r="BD4" t="n">
-        <v>427</v>
+        <v>53.25516260185486</v>
       </c>
       <c r="BE4" t="n">
-        <v>427</v>
+        <v>54.74205969818819</v>
       </c>
       <c r="BF4" t="n">
-        <v>427</v>
+        <v>57.32908838451907</v>
       </c>
       <c r="BG4" t="n">
-        <v>427</v>
+        <v>60.84671439824194</v>
       </c>
       <c r="BH4" t="n">
-        <v>427</v>
+        <v>63.02705272341394</v>
       </c>
       <c r="BI4" t="n">
-        <v>427</v>
+        <v>65.54929442793416</v>
       </c>
       <c r="BJ4" t="n">
-        <v>427</v>
+        <v>67.77840290239952</v>
       </c>
       <c r="BK4" t="n">
-        <v>635</v>
+        <v>358</v>
       </c>
       <c r="BL4" t="n">
-        <v>635</v>
+        <v>358</v>
       </c>
       <c r="BM4" t="n">
-        <v>635</v>
+        <v>358</v>
       </c>
       <c r="BN4" t="n">
-        <v>635</v>
+        <v>358</v>
       </c>
       <c r="BO4" t="n">
-        <v>635</v>
+        <v>358</v>
       </c>
       <c r="BP4" t="n">
-        <v>635</v>
+        <v>358</v>
       </c>
       <c r="BQ4" t="n">
-        <v>635</v>
+        <v>358</v>
       </c>
       <c r="BR4" t="n">
-        <v>635</v>
+        <v>358</v>
       </c>
       <c r="BS4" t="n">
-        <v>635</v>
+        <v>358</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.8</v>
+        <v>643</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.875</v>
+        <v>643</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.9</v>
+        <v>643</v>
       </c>
       <c r="BW4" t="n">
+        <v>643</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>643</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>643</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>643</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>643</v>
+      </c>
+      <c r="CB4" t="n">
+        <v>643</v>
+      </c>
+      <c r="CC4" t="n">
+        <v>0.3636363636363636</v>
+      </c>
+      <c r="CD4" t="n">
         <v>1</v>
       </c>
-      <c r="BX4" t="n">
-        <v>0.9444444444444444</v>
-      </c>
-      <c r="BY4" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="BZ4" t="n">
-        <v>0.9130434782608695</v>
-      </c>
-      <c r="CA4" t="n">
+      <c r="CE4" t="n">
+        <v>0.6470588235294118</v>
+      </c>
+      <c r="CF4" t="n">
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="CG4" t="n">
         <v>1</v>
       </c>
-      <c r="CB4" t="n">
-        <v>0.9666666666666667</v>
+      <c r="CH4" t="n">
+        <v>0.8260869565217391</v>
+      </c>
+      <c r="CI4" t="n">
+        <v>0.8076923076923077</v>
+      </c>
+      <c r="CJ4" t="n">
+        <v>0.71875</v>
+      </c>
+      <c r="CK4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="CL4" t="n">
+        <v>515.83</v>
+      </c>
+      <c r="CM4" t="n">
+        <v>76.93000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -1578,10 +1732,10 @@
         <v>499</v>
       </c>
       <c r="C5" t="n">
+        <v>85.9896219421794</v>
+      </c>
+      <c r="D5" t="n">
         <v>58</v>
-      </c>
-      <c r="D5" t="n">
-        <v>85.9896219421794</v>
       </c>
       <c r="E5" t="n">
         <v>499</v>
@@ -1590,244 +1744,277 @@
         <v>200</v>
       </c>
       <c r="G5" t="n">
-        <v>0.495</v>
-      </c>
-      <c r="H5" t="inlineStr">
+        <v>75.5</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="L5" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I5" t="n">
-        <v>511.5210574141663</v>
-      </c>
-      <c r="J5" t="n">
-        <v>56.8042815442123</v>
-      </c>
-      <c r="K5" t="n">
-        <v>489.3422318801568</v>
-      </c>
-      <c r="L5" t="n">
-        <v>75.16694632790256</v>
-      </c>
-      <c r="M5" t="n">
-        <v>493.2527279447526</v>
-      </c>
-      <c r="N5" t="n">
-        <v>59.30629867941599</v>
-      </c>
-      <c r="O5" t="n">
-        <v>490.9237273365025</v>
-      </c>
-      <c r="P5" t="n">
-        <v>53.6325899354477</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>494.6193678564269</v>
-      </c>
       <c r="R5" t="n">
-        <v>56.13166440894487</v>
+        <v>511.52</v>
       </c>
       <c r="S5" t="n">
-        <v>493.2033612973958</v>
+        <v>56.8</v>
       </c>
       <c r="T5" t="n">
-        <v>52.2760281341606</v>
+        <v>489.34</v>
       </c>
       <c r="U5" t="n">
-        <v>490.1807320026211</v>
+        <v>75.17</v>
       </c>
       <c r="V5" t="n">
-        <v>51.4225785597099</v>
+        <v>493.25</v>
       </c>
       <c r="W5" t="n">
-        <v>493.8465868984647</v>
+        <v>59.31</v>
       </c>
       <c r="X5" t="n">
-        <v>53.88327731630505</v>
+        <v>490.92</v>
       </c>
       <c r="Y5" t="n">
-        <v>496.5693258867889</v>
+        <v>53.63</v>
       </c>
       <c r="Z5" t="n">
-        <v>57.67961532144575</v>
+        <v>494.62</v>
       </c>
       <c r="AA5" t="n">
+        <v>56.13</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>493.2</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>52.28</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>490.18</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>51.42</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>493.85</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>53.88</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>496.57</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>57.68</v>
+      </c>
+      <c r="AJ5" t="n">
         <v>0</v>
       </c>
-      <c r="AB5" t="n">
+      <c r="AK5" t="n">
         <v>-0.1666666666666667</v>
       </c>
-      <c r="AC5" t="n">
+      <c r="AL5" t="n">
         <v>-0.125</v>
       </c>
-      <c r="AD5" t="n">
+      <c r="AM5" t="n">
         <v>-0.1</v>
       </c>
-      <c r="AE5" t="n">
+      <c r="AN5" t="n">
         <v>-0.06666666666666667</v>
       </c>
-      <c r="AF5" t="n">
+      <c r="AO5" t="n">
         <v>-0.05714285714285714</v>
       </c>
-      <c r="AG5" t="n">
+      <c r="AP5" t="n">
         <v>-0.05</v>
       </c>
-      <c r="AH5" t="n">
+      <c r="AQ5" t="n">
         <v>-0.04444444444444445</v>
       </c>
-      <c r="AI5" t="n">
+      <c r="AR5" t="n">
         <v>-0.04</v>
       </c>
-      <c r="AJ5" t="n">
+      <c r="AS5" t="n">
         <v>510.525</v>
       </c>
-      <c r="AK5" t="n">
+      <c r="AT5" t="n">
         <v>495.25</v>
       </c>
-      <c r="AL5" t="n">
+      <c r="AU5" t="n">
         <v>494.325</v>
       </c>
-      <c r="AM5" t="n">
+      <c r="AV5" t="n">
         <v>494.47</v>
       </c>
-      <c r="AN5" t="n">
+      <c r="AW5" t="n">
         <v>495.0666666666667</v>
       </c>
-      <c r="AO5" t="n">
+      <c r="AX5" t="n">
         <v>495.3642857142857</v>
       </c>
-      <c r="AP5" t="n">
+      <c r="AY5" t="n">
         <v>495.09375</v>
       </c>
-      <c r="AQ5" t="n">
+      <c r="AZ5" t="n">
         <v>495.4666666666666</v>
       </c>
-      <c r="AR5" t="n">
+      <c r="BA5" t="n">
         <v>495.54</v>
       </c>
-      <c r="AS5" t="n">
+      <c r="BB5" t="n">
         <v>59.80551291478069</v>
       </c>
-      <c r="AT5" t="n">
+      <c r="BC5" t="n">
         <v>65.33595870575407</v>
       </c>
-      <c r="AU5" t="n">
+      <c r="BD5" t="n">
         <v>66.67866506612141</v>
       </c>
-      <c r="AV5" t="n">
+      <c r="BE5" t="n">
         <v>63.38650566169428</v>
       </c>
-      <c r="AW5" t="n">
+      <c r="BF5" t="n">
         <v>61.77576835261182</v>
       </c>
-      <c r="AX5" t="n">
+      <c r="BG5" t="n">
         <v>60.09744595408429</v>
       </c>
-      <c r="AY5" t="n">
+      <c r="BH5" t="n">
         <v>58.16268099853634</v>
       </c>
-      <c r="AZ5" t="n">
+      <c r="BI5" t="n">
         <v>57.44943670548717</v>
       </c>
-      <c r="BA5" t="n">
+      <c r="BJ5" t="n">
         <v>56.4813987078932</v>
       </c>
-      <c r="BB5" t="n">
+      <c r="BK5" t="n">
         <v>350</v>
       </c>
-      <c r="BC5" t="n">
+      <c r="BL5" t="n">
         <v>350</v>
       </c>
-      <c r="BD5" t="n">
+      <c r="BM5" t="n">
         <v>350</v>
       </c>
-      <c r="BE5" t="n">
+      <c r="BN5" t="n">
         <v>350</v>
       </c>
-      <c r="BF5" t="n">
+      <c r="BO5" t="n">
         <v>350</v>
       </c>
-      <c r="BG5" t="n">
+      <c r="BP5" t="n">
         <v>350</v>
       </c>
-      <c r="BH5" t="n">
+      <c r="BQ5" t="n">
         <v>350</v>
       </c>
-      <c r="BI5" t="n">
+      <c r="BR5" t="n">
         <v>350</v>
       </c>
-      <c r="BJ5" t="n">
+      <c r="BS5" t="n">
         <v>350</v>
       </c>
-      <c r="BK5" t="n">
+      <c r="BT5" t="n">
         <v>607</v>
       </c>
-      <c r="BL5" t="n">
+      <c r="BU5" t="n">
         <v>607</v>
       </c>
-      <c r="BM5" t="n">
+      <c r="BV5" t="n">
         <v>607</v>
       </c>
-      <c r="BN5" t="n">
+      <c r="BW5" t="n">
         <v>607</v>
       </c>
-      <c r="BO5" t="n">
+      <c r="BX5" t="n">
         <v>607</v>
       </c>
-      <c r="BP5" t="n">
+      <c r="BY5" t="n">
         <v>607</v>
       </c>
-      <c r="BQ5" t="n">
+      <c r="BZ5" t="n">
         <v>607</v>
       </c>
-      <c r="BR5" t="n">
+      <c r="CA5" t="n">
         <v>607</v>
       </c>
-      <c r="BS5" t="n">
+      <c r="CB5" t="n">
         <v>607</v>
       </c>
-      <c r="BT5" t="n">
+      <c r="CC5" t="n">
         <v>1</v>
       </c>
-      <c r="BU5" t="n">
+      <c r="CD5" t="n">
         <v>1</v>
       </c>
-      <c r="BV5" t="n">
+      <c r="CE5" t="n">
         <v>0.8333333333333334</v>
       </c>
-      <c r="BW5" t="n">
+      <c r="CF5" t="n">
         <v>0.9230769230769231</v>
       </c>
-      <c r="BX5" t="n">
+      <c r="CG5" t="n">
         <v>1</v>
       </c>
-      <c r="BY5" t="n">
+      <c r="CH5" t="n">
         <v>0.2105263157894737</v>
       </c>
-      <c r="BZ5" t="n">
+      <c r="CI5" t="n">
         <v>0.1666666666666667</v>
       </c>
-      <c r="CA5" t="n">
+      <c r="CJ5" t="n">
         <v>0.9</v>
       </c>
-      <c r="CB5" t="n">
+      <c r="CK5" t="n">
         <v>0.9411764705882353</v>
+      </c>
+      <c r="CL5" t="n">
+        <v>496.57</v>
+      </c>
+      <c r="CM5" t="n">
+        <v>57.68</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S06_G6_499_60_ABS1</t>
+          <t>S05_G6_499_58_ABS1</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>499</v>
       </c>
       <c r="C6" t="n">
-        <v>60</v>
+        <v>85.9896219421794</v>
       </c>
       <c r="D6" t="n">
-        <v>88.95478131949592</v>
+        <v>58</v>
       </c>
       <c r="E6" t="n">
         <v>499</v>
@@ -1836,244 +2023,277 @@
         <v>200</v>
       </c>
       <c r="G6" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="H6" t="inlineStr">
+        <v>76</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="Q6" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I6" t="n">
-        <v>503.1864029386311</v>
-      </c>
-      <c r="J6" t="n">
-        <v>119.0725383776088</v>
-      </c>
-      <c r="K6" t="n">
-        <v>491.5392659247374</v>
-      </c>
-      <c r="L6" t="n">
-        <v>94.96736961267662</v>
-      </c>
-      <c r="M6" t="n">
-        <v>483.0425659833741</v>
-      </c>
-      <c r="N6" t="n">
-        <v>87.47606651753017</v>
-      </c>
-      <c r="O6" t="n">
-        <v>483.2902531079512</v>
-      </c>
-      <c r="P6" t="n">
-        <v>77.27228903962177</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>489.3804690278924</v>
-      </c>
       <c r="R6" t="n">
-        <v>75.36186685228864</v>
+        <v>522.52</v>
       </c>
       <c r="S6" t="n">
-        <v>486.8009942501475</v>
+        <v>25.27</v>
       </c>
       <c r="T6" t="n">
-        <v>84.20142720021357</v>
+        <v>514.41</v>
       </c>
       <c r="U6" t="n">
-        <v>487.9612108149119</v>
+        <v>47.72</v>
       </c>
       <c r="V6" t="n">
-        <v>81.42345169878342</v>
+        <v>513.0599999999999</v>
       </c>
       <c r="W6" t="n">
-        <v>490.9369367935687</v>
+        <v>43.18</v>
       </c>
       <c r="X6" t="n">
-        <v>78.15393732182359</v>
+        <v>518.84</v>
       </c>
       <c r="Y6" t="n">
-        <v>494.2216710525882</v>
+        <v>48.54</v>
       </c>
       <c r="Z6" t="n">
-        <v>80.47352897346623</v>
+        <v>522.22</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0.1</v>
+        <v>54.82</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0.1</v>
+        <v>517.03</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.1</v>
+        <v>53.71</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0.08</v>
+        <v>514.15</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0.06666666666666667</v>
+        <v>56.73</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.05714285714285714</v>
+        <v>510.07</v>
       </c>
       <c r="AG6" t="n">
-        <v>-0.0375</v>
+        <v>60.96</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0.04444444444444445</v>
+        <v>510.22</v>
       </c>
       <c r="AI6" t="n">
-        <v>-0.03</v>
+        <v>55.57</v>
       </c>
       <c r="AJ6" t="n">
-        <v>479.475</v>
+        <v>0.5897435897435898</v>
       </c>
       <c r="AK6" t="n">
-        <v>483.5833333333333</v>
+        <v>0.2542372881355932</v>
       </c>
       <c r="AL6" t="n">
-        <v>481.975</v>
+        <v>0.1645569620253164</v>
       </c>
       <c r="AM6" t="n">
-        <v>482.39</v>
+        <v>0.1717171717171717</v>
       </c>
       <c r="AN6" t="n">
-        <v>482.975</v>
+        <v>0.2100840336134454</v>
       </c>
       <c r="AO6" t="n">
-        <v>483.6142857142857</v>
+        <v>0.1510791366906475</v>
       </c>
       <c r="AP6" t="n">
-        <v>484.9</v>
+        <v>0.08176100628930817</v>
       </c>
       <c r="AQ6" t="n">
-        <v>484.6166666666667</v>
+        <v>0.03910614525139665</v>
       </c>
       <c r="AR6" t="n">
-        <v>486.515</v>
+        <v>0.05527638190954774</v>
       </c>
       <c r="AS6" t="n">
-        <v>83.06713775615481</v>
+        <v>523.6</v>
       </c>
       <c r="AT6" t="n">
-        <v>81.08478929833608</v>
+        <v>515.0833333333334</v>
       </c>
       <c r="AU6" t="n">
-        <v>81.11719531024232</v>
+        <v>513.925</v>
       </c>
       <c r="AV6" t="n">
-        <v>81.1626632140666</v>
+        <v>517.21</v>
       </c>
       <c r="AW6" t="n">
-        <v>79.62374671959783</v>
+        <v>522.0916666666667</v>
       </c>
       <c r="AX6" t="n">
-        <v>79.81045274490641</v>
+        <v>520.3785714285714</v>
       </c>
       <c r="AY6" t="n">
-        <v>80.90659738241375</v>
+        <v>516.09375</v>
       </c>
       <c r="AZ6" t="n">
-        <v>80.42037297158531</v>
+        <v>513.5111111111111</v>
       </c>
       <c r="BA6" t="n">
-        <v>80.22923267114052</v>
+        <v>514.23</v>
       </c>
       <c r="BB6" t="n">
-        <v>273</v>
+        <v>31.97717936278933</v>
       </c>
       <c r="BC6" t="n">
-        <v>273</v>
+        <v>41.39174300375485</v>
       </c>
       <c r="BD6" t="n">
-        <v>273</v>
+        <v>44.69893035632956</v>
       </c>
       <c r="BE6" t="n">
-        <v>273</v>
+        <v>45.87707379508855</v>
       </c>
       <c r="BF6" t="n">
-        <v>273</v>
+        <v>49.18349923726679</v>
       </c>
       <c r="BG6" t="n">
-        <v>273</v>
+        <v>50.25328245954869</v>
       </c>
       <c r="BH6" t="n">
-        <v>273</v>
+        <v>52.50795140678695</v>
       </c>
       <c r="BI6" t="n">
-        <v>273</v>
+        <v>54.5215032898732</v>
       </c>
       <c r="BJ6" t="n">
-        <v>273</v>
+        <v>55.05767067357645</v>
       </c>
       <c r="BK6" t="n">
-        <v>596</v>
+        <v>456</v>
       </c>
       <c r="BL6" t="n">
-        <v>596</v>
+        <v>441</v>
       </c>
       <c r="BM6" t="n">
-        <v>596</v>
+        <v>441</v>
       </c>
       <c r="BN6" t="n">
-        <v>596</v>
+        <v>441</v>
       </c>
       <c r="BO6" t="n">
-        <v>596</v>
+        <v>441</v>
       </c>
       <c r="BP6" t="n">
-        <v>596</v>
+        <v>441</v>
       </c>
       <c r="BQ6" t="n">
-        <v>596</v>
+        <v>436</v>
       </c>
       <c r="BR6" t="n">
-        <v>596</v>
+        <v>435</v>
       </c>
       <c r="BS6" t="n">
-        <v>596</v>
+        <v>435</v>
       </c>
       <c r="BT6" t="n">
-        <v>0.5</v>
+        <v>636</v>
       </c>
       <c r="BU6" t="n">
-        <v>0.9</v>
+        <v>636</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.7142857142857143</v>
+        <v>636</v>
       </c>
       <c r="BW6" t="n">
-        <v>0.7368421052631579</v>
+        <v>636</v>
       </c>
       <c r="BX6" t="n">
-        <v>0.9545454545454546</v>
+        <v>636</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.1739130434782609</v>
+        <v>636</v>
       </c>
       <c r="BZ6" t="n">
+        <v>636</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>636</v>
+      </c>
+      <c r="CB6" t="n">
+        <v>636</v>
+      </c>
+      <c r="CC6" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="CD6" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE6" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="CF6" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG6" t="n">
+        <v>0.9285714285714286</v>
+      </c>
+      <c r="CH6" t="n">
+        <v>1</v>
+      </c>
+      <c r="CI6" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ6" t="n">
+        <v>0.9565217391304348</v>
+      </c>
+      <c r="CK6" t="n">
         <v>0.8620689655172413</v>
       </c>
-      <c r="CA6" t="n">
-        <v>1</v>
-      </c>
-      <c r="CB6" t="n">
-        <v>0.926829268292683</v>
+      <c r="CL6" t="n">
+        <v>510.22</v>
+      </c>
+      <c r="CM6" t="n">
+        <v>55.57</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S05_G6_499_58_ABS1</t>
+          <t>S06_G6_499_60_ABS1</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>499</v>
       </c>
       <c r="C7" t="n">
-        <v>58</v>
+        <v>88.95478131949592</v>
       </c>
       <c r="D7" t="n">
-        <v>85.9896219421794</v>
+        <v>60</v>
       </c>
       <c r="E7" t="n">
         <v>499</v>
@@ -2082,228 +2302,261 @@
         <v>200</v>
       </c>
       <c r="G7" t="n">
-        <v>0.515</v>
-      </c>
-      <c r="H7" t="inlineStr">
+        <v>77.5</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="M7" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="N7" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I7" t="n">
-        <v>522.522842293701</v>
-      </c>
-      <c r="J7" t="n">
-        <v>25.27271736269831</v>
-      </c>
-      <c r="K7" t="n">
-        <v>514.4094986353863</v>
-      </c>
-      <c r="L7" t="n">
-        <v>47.7185356841519</v>
-      </c>
-      <c r="M7" t="n">
-        <v>513.0621574162285</v>
-      </c>
-      <c r="N7" t="n">
-        <v>43.18189576019461</v>
-      </c>
-      <c r="O7" t="n">
-        <v>518.8447680748034</v>
-      </c>
-      <c r="P7" t="n">
-        <v>48.54028933008558</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>522.2248047676009</v>
-      </c>
       <c r="R7" t="n">
-        <v>54.82117803845103</v>
+        <v>503.19</v>
       </c>
       <c r="S7" t="n">
-        <v>517.027451958852</v>
+        <v>119.07</v>
       </c>
       <c r="T7" t="n">
-        <v>53.71156574420134</v>
+        <v>491.54</v>
       </c>
       <c r="U7" t="n">
-        <v>514.1510940465582</v>
+        <v>94.97</v>
       </c>
       <c r="V7" t="n">
-        <v>56.72809465303626</v>
+        <v>483.04</v>
       </c>
       <c r="W7" t="n">
-        <v>510.0686183779053</v>
+        <v>87.48</v>
       </c>
       <c r="X7" t="n">
-        <v>60.95656892261255</v>
+        <v>483.29</v>
       </c>
       <c r="Y7" t="n">
-        <v>510.2188203317805</v>
+        <v>77.27</v>
       </c>
       <c r="Z7" t="n">
-        <v>55.5681841897541</v>
+        <v>489.38</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.5897435897435898</v>
+        <v>75.36</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.2542372881355932</v>
+        <v>486.8</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.1645569620253164</v>
+        <v>84.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.1717171717171717</v>
+        <v>487.96</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.2100840336134454</v>
+        <v>81.42</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.1510791366906475</v>
+        <v>490.94</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.08176100628930817</v>
+        <v>78.15000000000001</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.03910614525139665</v>
+        <v>494.22</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.05527638190954774</v>
+        <v>80.47</v>
       </c>
       <c r="AJ7" t="n">
-        <v>523.6</v>
+        <v>-0.1</v>
       </c>
       <c r="AK7" t="n">
-        <v>515.0833333333334</v>
+        <v>-0.1</v>
       </c>
       <c r="AL7" t="n">
-        <v>513.925</v>
+        <v>-0.1</v>
       </c>
       <c r="AM7" t="n">
-        <v>517.21</v>
+        <v>-0.08</v>
       </c>
       <c r="AN7" t="n">
-        <v>522.0916666666667</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="AO7" t="n">
-        <v>520.3785714285714</v>
+        <v>-0.05714285714285714</v>
       </c>
       <c r="AP7" t="n">
-        <v>516.09375</v>
+        <v>-0.0375</v>
       </c>
       <c r="AQ7" t="n">
-        <v>513.5111111111111</v>
+        <v>-0.04444444444444445</v>
       </c>
       <c r="AR7" t="n">
-        <v>514.23</v>
+        <v>-0.03</v>
       </c>
       <c r="AS7" t="n">
-        <v>31.97717936278933</v>
+        <v>479.475</v>
       </c>
       <c r="AT7" t="n">
-        <v>41.39174300375485</v>
+        <v>483.5833333333333</v>
       </c>
       <c r="AU7" t="n">
-        <v>44.69893035632956</v>
+        <v>481.975</v>
       </c>
       <c r="AV7" t="n">
-        <v>45.87707379508855</v>
+        <v>482.39</v>
       </c>
       <c r="AW7" t="n">
-        <v>49.18349923726679</v>
+        <v>482.975</v>
       </c>
       <c r="AX7" t="n">
-        <v>50.25328245954869</v>
+        <v>483.6142857142857</v>
       </c>
       <c r="AY7" t="n">
-        <v>52.50795140678695</v>
+        <v>484.9</v>
       </c>
       <c r="AZ7" t="n">
-        <v>54.5215032898732</v>
+        <v>484.6166666666667</v>
       </c>
       <c r="BA7" t="n">
-        <v>55.05767067357645</v>
+        <v>486.515</v>
       </c>
       <c r="BB7" t="n">
-        <v>456</v>
+        <v>83.06713775615481</v>
       </c>
       <c r="BC7" t="n">
-        <v>441</v>
+        <v>81.08478929833608</v>
       </c>
       <c r="BD7" t="n">
-        <v>441</v>
+        <v>81.11719531024232</v>
       </c>
       <c r="BE7" t="n">
-        <v>441</v>
+        <v>81.1626632140666</v>
       </c>
       <c r="BF7" t="n">
-        <v>441</v>
+        <v>79.62374671959783</v>
       </c>
       <c r="BG7" t="n">
-        <v>441</v>
+        <v>79.81045274490641</v>
       </c>
       <c r="BH7" t="n">
-        <v>436</v>
+        <v>80.90659738241375</v>
       </c>
       <c r="BI7" t="n">
-        <v>435</v>
+        <v>80.42037297158531</v>
       </c>
       <c r="BJ7" t="n">
-        <v>435</v>
+        <v>80.22923267114052</v>
       </c>
       <c r="BK7" t="n">
-        <v>636</v>
+        <v>273</v>
       </c>
       <c r="BL7" t="n">
-        <v>636</v>
+        <v>273</v>
       </c>
       <c r="BM7" t="n">
-        <v>636</v>
+        <v>273</v>
       </c>
       <c r="BN7" t="n">
-        <v>636</v>
+        <v>273</v>
       </c>
       <c r="BO7" t="n">
-        <v>636</v>
+        <v>273</v>
       </c>
       <c r="BP7" t="n">
-        <v>636</v>
+        <v>273</v>
       </c>
       <c r="BQ7" t="n">
-        <v>636</v>
+        <v>273</v>
       </c>
       <c r="BR7" t="n">
-        <v>636</v>
+        <v>273</v>
       </c>
       <c r="BS7" t="n">
-        <v>636</v>
+        <v>273</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.8571428571428571</v>
+        <v>596</v>
       </c>
       <c r="BU7" t="n">
+        <v>596</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>596</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>596</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>596</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>596</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>596</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>596</v>
+      </c>
+      <c r="CB7" t="n">
+        <v>596</v>
+      </c>
+      <c r="CC7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="CD7" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="CE7" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="CF7" t="n">
+        <v>0.7368421052631579</v>
+      </c>
+      <c r="CG7" t="n">
+        <v>0.9545454545454546</v>
+      </c>
+      <c r="CH7" t="n">
+        <v>0.1739130434782609</v>
+      </c>
+      <c r="CI7" t="n">
+        <v>0.8620689655172413</v>
+      </c>
+      <c r="CJ7" t="n">
         <v>1</v>
       </c>
-      <c r="BV7" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>1</v>
-      </c>
-      <c r="BX7" t="n">
-        <v>0.9285714285714286</v>
-      </c>
-      <c r="BY7" t="n">
-        <v>1</v>
-      </c>
-      <c r="BZ7" t="n">
-        <v>1</v>
-      </c>
-      <c r="CA7" t="n">
-        <v>0.9565217391304348</v>
-      </c>
-      <c r="CB7" t="n">
-        <v>0.8620689655172413</v>
+      <c r="CK7" t="n">
+        <v>0.926829268292683</v>
+      </c>
+      <c r="CL7" t="n">
+        <v>494.22</v>
+      </c>
+      <c r="CM7" t="n">
+        <v>80.47</v>
       </c>
     </row>
     <row r="8">
@@ -2316,10 +2569,10 @@
         <v>502</v>
       </c>
       <c r="C8" t="n">
+        <v>91.91994069681246</v>
+      </c>
+      <c r="D8" t="n">
         <v>62</v>
-      </c>
-      <c r="D8" t="n">
-        <v>91.91994069681246</v>
       </c>
       <c r="E8" t="n">
         <v>502</v>
@@ -2328,228 +2581,261 @@
         <v>200</v>
       </c>
       <c r="G8" t="n">
-        <v>0.495</v>
-      </c>
-      <c r="H8" t="inlineStr">
+        <v>77.5</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="Q8" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I8" t="n">
-        <v>513.0390947568798</v>
-      </c>
-      <c r="J8" t="n">
-        <v>55.195080848186</v>
-      </c>
-      <c r="K8" t="n">
-        <v>508.6371072521281</v>
-      </c>
-      <c r="L8" t="n">
-        <v>59.4339513240688</v>
-      </c>
-      <c r="M8" t="n">
-        <v>510.0832343737324</v>
-      </c>
-      <c r="N8" t="n">
-        <v>83.46600838575078</v>
-      </c>
-      <c r="O8" t="n">
-        <v>504.002105407949</v>
-      </c>
-      <c r="P8" t="n">
-        <v>85.03144557228948</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>506.4183198384094</v>
-      </c>
       <c r="R8" t="n">
-        <v>73.1949877094053</v>
+        <v>513.04</v>
       </c>
       <c r="S8" t="n">
-        <v>507.8523766465323</v>
+        <v>55.2</v>
       </c>
       <c r="T8" t="n">
-        <v>72.25006754720577</v>
+        <v>508.64</v>
       </c>
       <c r="U8" t="n">
-        <v>508.3632244995474</v>
+        <v>59.43</v>
       </c>
       <c r="V8" t="n">
-        <v>72.17053890163874</v>
+        <v>510.08</v>
       </c>
       <c r="W8" t="n">
-        <v>510.2479751863044</v>
+        <v>83.47</v>
       </c>
       <c r="X8" t="n">
-        <v>72.79175107857543</v>
+        <v>504</v>
       </c>
       <c r="Y8" t="n">
-        <v>508.4752482445177</v>
+        <v>85.03</v>
       </c>
       <c r="Z8" t="n">
-        <v>70.74843882650038</v>
+        <v>506.42</v>
       </c>
       <c r="AA8" t="n">
+        <v>73.19</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>507.85</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>72.25</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>508.36</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>72.17</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>510.25</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>72.79000000000001</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>508.48</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>70.75</v>
+      </c>
+      <c r="AJ8" t="n">
         <v>0.05</v>
       </c>
-      <c r="AB8" t="n">
+      <c r="AK8" t="n">
         <v>0</v>
       </c>
-      <c r="AC8" t="n">
+      <c r="AL8" t="n">
         <v>-0.025</v>
       </c>
-      <c r="AD8" t="n">
+      <c r="AM8" t="n">
         <v>-0.04</v>
       </c>
-      <c r="AE8" t="n">
+      <c r="AN8" t="n">
         <v>-0.01666666666666667</v>
       </c>
-      <c r="AF8" t="n">
+      <c r="AO8" t="n">
         <v>-0.02857142857142857</v>
       </c>
-      <c r="AG8" t="n">
+      <c r="AP8" t="n">
         <v>-0.025</v>
       </c>
-      <c r="AH8" t="n">
+      <c r="AQ8" t="n">
         <v>-0.02222222222222222</v>
       </c>
-      <c r="AI8" t="n">
+      <c r="AR8" t="n">
         <v>-0.02</v>
       </c>
-      <c r="AJ8" t="n">
+      <c r="AS8" t="n">
         <v>511.525</v>
       </c>
-      <c r="AK8" t="n">
+      <c r="AT8" t="n">
         <v>508.25</v>
       </c>
-      <c r="AL8" t="n">
+      <c r="AU8" t="n">
         <v>506.0625</v>
       </c>
-      <c r="AM8" t="n">
+      <c r="AV8" t="n">
         <v>504.24</v>
       </c>
-      <c r="AN8" t="n">
+      <c r="AW8" t="n">
         <v>506.45</v>
       </c>
-      <c r="AO8" t="n">
+      <c r="AX8" t="n">
         <v>505.8928571428572</v>
       </c>
-      <c r="AP8" t="n">
+      <c r="AY8" t="n">
         <v>506.6375</v>
       </c>
-      <c r="AQ8" t="n">
+      <c r="AZ8" t="n">
         <v>506.9055555555556</v>
       </c>
-      <c r="AR8" t="n">
+      <c r="BA8" t="n">
         <v>507.125</v>
       </c>
-      <c r="AS8" t="n">
+      <c r="BB8" t="n">
         <v>61.21927290486224</v>
       </c>
-      <c r="AT8" t="n">
+      <c r="BC8" t="n">
         <v>61.17887026307912</v>
       </c>
-      <c r="AU8" t="n">
+      <c r="BD8" t="n">
         <v>66.6855201205629</v>
       </c>
-      <c r="AV8" t="n">
+      <c r="BE8" t="n">
         <v>72.67793612919949</v>
       </c>
-      <c r="AW8" t="n">
+      <c r="BF8" t="n">
         <v>74.85439755507576</v>
       </c>
-      <c r="AX8" t="n">
+      <c r="BG8" t="n">
         <v>74.20412930641022</v>
       </c>
-      <c r="AY8" t="n">
+      <c r="BH8" t="n">
         <v>74.0060375493108</v>
       </c>
-      <c r="AZ8" t="n">
+      <c r="BI8" t="n">
         <v>73.211314943815</v>
       </c>
-      <c r="BA8" t="n">
+      <c r="BJ8" t="n">
         <v>72.66085173599329</v>
       </c>
-      <c r="BB8" t="n">
+      <c r="BK8" t="n">
         <v>353</v>
       </c>
-      <c r="BC8" t="n">
+      <c r="BL8" t="n">
         <v>353</v>
       </c>
-      <c r="BD8" t="n">
+      <c r="BM8" t="n">
         <v>353</v>
       </c>
-      <c r="BE8" t="n">
+      <c r="BN8" t="n">
         <v>353</v>
       </c>
-      <c r="BF8" t="n">
+      <c r="BO8" t="n">
         <v>353</v>
       </c>
-      <c r="BG8" t="n">
+      <c r="BP8" t="n">
         <v>353</v>
       </c>
-      <c r="BH8" t="n">
+      <c r="BQ8" t="n">
         <v>353</v>
       </c>
-      <c r="BI8" t="n">
+      <c r="BR8" t="n">
         <v>353</v>
       </c>
-      <c r="BJ8" t="n">
+      <c r="BS8" t="n">
         <v>353</v>
       </c>
-      <c r="BK8" t="n">
+      <c r="BT8" t="n">
         <v>610</v>
       </c>
-      <c r="BL8" t="n">
+      <c r="BU8" t="n">
         <v>610</v>
       </c>
-      <c r="BM8" t="n">
+      <c r="BV8" t="n">
         <v>610</v>
       </c>
-      <c r="BN8" t="n">
+      <c r="BW8" t="n">
         <v>610</v>
       </c>
-      <c r="BO8" t="n">
+      <c r="BX8" t="n">
         <v>610</v>
       </c>
-      <c r="BP8" t="n">
+      <c r="BY8" t="n">
         <v>610</v>
       </c>
-      <c r="BQ8" t="n">
+      <c r="BZ8" t="n">
         <v>610</v>
       </c>
-      <c r="BR8" t="n">
+      <c r="CA8" t="n">
         <v>610</v>
       </c>
-      <c r="BS8" t="n">
+      <c r="CB8" t="n">
         <v>610</v>
       </c>
-      <c r="BT8" t="n">
+      <c r="CC8" t="n">
         <v>0.8333333333333334</v>
       </c>
-      <c r="BU8" t="n">
+      <c r="CD8" t="n">
         <v>0</v>
       </c>
-      <c r="BV8" t="n">
+      <c r="CE8" t="n">
         <v>1</v>
       </c>
-      <c r="BW8" t="n">
+      <c r="CF8" t="n">
         <v>0.9090909090909091</v>
       </c>
-      <c r="BX8" t="n">
+      <c r="CG8" t="n">
         <v>0.7647058823529411</v>
       </c>
-      <c r="BY8" t="n">
+      <c r="CH8" t="n">
         <v>0.9</v>
       </c>
-      <c r="BZ8" t="n">
+      <c r="CI8" t="n">
         <v>0</v>
       </c>
-      <c r="CA8" t="n">
+      <c r="CJ8" t="n">
         <v>1</v>
       </c>
-      <c r="CB8" t="n">
+      <c r="CK8" t="n">
         <v>0.9428571428571428</v>
+      </c>
+      <c r="CL8" t="n">
+        <v>508.48</v>
+      </c>
+      <c r="CM8" t="n">
+        <v>70.75</v>
       </c>
     </row>
     <row r="9">
@@ -2562,10 +2848,10 @@
         <v>502</v>
       </c>
       <c r="C9" t="n">
+        <v>87.47220163083766</v>
+      </c>
+      <c r="D9" t="n">
         <v>59</v>
-      </c>
-      <c r="D9" t="n">
-        <v>87.47220163083766</v>
       </c>
       <c r="E9" t="n">
         <v>502</v>
@@ -2574,228 +2860,261 @@
         <v>200</v>
       </c>
       <c r="G9" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="H9" t="inlineStr">
+        <v>76.5</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I9" t="n">
-        <v>493.7158822999178</v>
-      </c>
-      <c r="J9" t="n">
-        <v>40.72726908549457</v>
-      </c>
-      <c r="K9" t="n">
-        <v>509.5517568104402</v>
-      </c>
-      <c r="L9" t="n">
-        <v>51.8291760802415</v>
-      </c>
-      <c r="M9" t="n">
-        <v>513.107011580211</v>
-      </c>
-      <c r="N9" t="n">
-        <v>62.78940213478351</v>
-      </c>
-      <c r="O9" t="n">
-        <v>515.4770798771169</v>
-      </c>
-      <c r="P9" t="n">
-        <v>69.67637353884865</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>513.4689959004583</v>
-      </c>
       <c r="R9" t="n">
-        <v>72.7129766499736</v>
+        <v>493.72</v>
       </c>
       <c r="S9" t="n">
-        <v>509.3354189026859</v>
+        <v>40.73</v>
       </c>
       <c r="T9" t="n">
-        <v>74.91016224143952</v>
+        <v>509.55</v>
       </c>
       <c r="U9" t="n">
-        <v>509.2355166590034</v>
+        <v>51.83</v>
       </c>
       <c r="V9" t="n">
-        <v>75.15067217202019</v>
+        <v>513.11</v>
       </c>
       <c r="W9" t="n">
-        <v>507.3605835329828</v>
+        <v>62.79</v>
       </c>
       <c r="X9" t="n">
-        <v>68.3738409058306</v>
+        <v>515.48</v>
       </c>
       <c r="Y9" t="n">
-        <v>501.0562638413703</v>
+        <v>69.68000000000001</v>
       </c>
       <c r="Z9" t="n">
-        <v>71.67341927952525</v>
+        <v>513.47</v>
       </c>
       <c r="AA9" t="n">
+        <v>72.70999999999999</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>509.34</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>74.91</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>509.24</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>75.15000000000001</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>507.36</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>68.37</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>501.06</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>71.67</v>
+      </c>
+      <c r="AJ9" t="n">
         <v>-0.15</v>
       </c>
-      <c r="AB9" t="n">
+      <c r="AK9" t="n">
         <v>0.03333333333333333</v>
       </c>
-      <c r="AC9" t="n">
+      <c r="AL9" t="n">
         <v>0.075</v>
       </c>
-      <c r="AD9" t="n">
+      <c r="AM9" t="n">
         <v>0.08</v>
       </c>
-      <c r="AE9" t="n">
+      <c r="AN9" t="n">
         <v>0.05</v>
       </c>
-      <c r="AF9" t="n">
+      <c r="AO9" t="n">
         <v>0.02857142857142857</v>
       </c>
-      <c r="AG9" t="n">
+      <c r="AP9" t="n">
         <v>0.025</v>
       </c>
-      <c r="AH9" t="n">
+      <c r="AQ9" t="n">
         <v>0.02222222222222222</v>
       </c>
-      <c r="AI9" t="n">
+      <c r="AR9" t="n">
         <v>0.01</v>
       </c>
-      <c r="AJ9" t="n">
+      <c r="AS9" t="n">
         <v>490.85</v>
       </c>
-      <c r="AK9" t="n">
+      <c r="AT9" t="n">
         <v>503.25</v>
       </c>
-      <c r="AL9" t="n">
+      <c r="AU9" t="n">
         <v>507.9625</v>
       </c>
-      <c r="AM9" t="n">
+      <c r="AV9" t="n">
         <v>511.44</v>
       </c>
-      <c r="AN9" t="n">
+      <c r="AW9" t="n">
         <v>510.25</v>
       </c>
-      <c r="AO9" t="n">
+      <c r="AX9" t="n">
         <v>508.9428571428571</v>
       </c>
-      <c r="AP9" t="n">
+      <c r="AY9" t="n">
         <v>508.8875</v>
       </c>
-      <c r="AQ9" t="n">
+      <c r="AZ9" t="n">
         <v>508.6944444444445</v>
       </c>
-      <c r="AR9" t="n">
+      <c r="BA9" t="n">
         <v>507.235</v>
       </c>
-      <c r="AS9" t="n">
+      <c r="BB9" t="n">
         <v>50.79938483879505</v>
       </c>
-      <c r="AT9" t="n">
+      <c r="BC9" t="n">
         <v>56.53483439438025</v>
       </c>
-      <c r="AU9" t="n">
+      <c r="BD9" t="n">
         <v>59.07568106886284</v>
       </c>
-      <c r="AV9" t="n">
+      <c r="BE9" t="n">
         <v>64.03472807781728</v>
       </c>
-      <c r="AW9" t="n">
+      <c r="BF9" t="n">
         <v>66.48047959113011</v>
       </c>
-      <c r="AX9" t="n">
+      <c r="BG9" t="n">
         <v>69.66837481224599</v>
       </c>
-      <c r="AY9" t="n">
+      <c r="BH9" t="n">
         <v>71.52997514154468</v>
       </c>
-      <c r="AZ9" t="n">
+      <c r="BI9" t="n">
         <v>71.53430390940048</v>
       </c>
-      <c r="BA9" t="n">
+      <c r="BJ9" t="n">
         <v>71.05265494687724</v>
       </c>
-      <c r="BB9" t="n">
+      <c r="BK9" t="n">
         <v>350</v>
       </c>
-      <c r="BC9" t="n">
+      <c r="BL9" t="n">
         <v>350</v>
       </c>
-      <c r="BD9" t="n">
+      <c r="BM9" t="n">
         <v>350</v>
       </c>
-      <c r="BE9" t="n">
+      <c r="BN9" t="n">
         <v>350</v>
       </c>
-      <c r="BF9" t="n">
+      <c r="BO9" t="n">
         <v>350</v>
       </c>
-      <c r="BG9" t="n">
+      <c r="BP9" t="n">
         <v>350</v>
       </c>
-      <c r="BH9" t="n">
+      <c r="BQ9" t="n">
         <v>350</v>
       </c>
-      <c r="BI9" t="n">
+      <c r="BR9" t="n">
         <v>350</v>
       </c>
-      <c r="BJ9" t="n">
+      <c r="BS9" t="n">
         <v>350</v>
       </c>
-      <c r="BK9" t="n">
+      <c r="BT9" t="n">
         <v>569</v>
       </c>
-      <c r="BL9" t="n">
+      <c r="BU9" t="n">
         <v>583</v>
       </c>
-      <c r="BM9" t="n">
+      <c r="BV9" t="n">
         <v>590</v>
       </c>
-      <c r="BN9" t="n">
+      <c r="BW9" t="n">
         <v>620</v>
       </c>
-      <c r="BO9" t="n">
+      <c r="BX9" t="n">
         <v>620</v>
       </c>
-      <c r="BP9" t="n">
+      <c r="BY9" t="n">
         <v>620</v>
       </c>
-      <c r="BQ9" t="n">
+      <c r="BZ9" t="n">
         <v>620</v>
       </c>
-      <c r="BR9" t="n">
+      <c r="CA9" t="n">
         <v>620</v>
       </c>
-      <c r="BS9" t="n">
+      <c r="CB9" t="n">
         <v>620</v>
       </c>
-      <c r="BT9" t="n">
+      <c r="CC9" t="n">
         <v>1</v>
       </c>
-      <c r="BU9" t="n">
+      <c r="CD9" t="n">
         <v>1</v>
       </c>
-      <c r="BV9" t="n">
+      <c r="CE9" t="n">
         <v>1</v>
       </c>
-      <c r="BW9" t="n">
+      <c r="CF9" t="n">
         <v>0.7619047619047619</v>
       </c>
-      <c r="BX9" t="n">
+      <c r="CG9" t="n">
         <v>0.6538461538461539</v>
       </c>
-      <c r="BY9" t="n">
+      <c r="CH9" t="n">
         <v>0.2857142857142857</v>
       </c>
-      <c r="BZ9" t="n">
+      <c r="CI9" t="n">
         <v>0.7241379310344828</v>
       </c>
-      <c r="CA9" t="n">
+      <c r="CJ9" t="n">
         <v>0.8235294117647058</v>
       </c>
-      <c r="CB9" t="n">
+      <c r="CK9" t="n">
         <v>0.6829268292682927</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>501.06</v>
+      </c>
+      <c r="CM9" t="n">
+        <v>71.67</v>
       </c>
     </row>
     <row r="10">
@@ -2808,10 +3127,10 @@
         <v>498</v>
       </c>
       <c r="C10" t="n">
+        <v>90.43736100815418</v>
+      </c>
+      <c r="D10" t="n">
         <v>61</v>
-      </c>
-      <c r="D10" t="n">
-        <v>90.43736100815418</v>
       </c>
       <c r="E10" t="n">
         <v>498</v>
@@ -2820,720 +3139,819 @@
         <v>200</v>
       </c>
       <c r="G10" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="H10" t="inlineStr">
+        <v>74</v>
+      </c>
+      <c r="H10" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="L10" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="O10" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="P10" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="Q10" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I10" t="n">
-        <v>529.2431275950346</v>
-      </c>
-      <c r="J10" t="n">
-        <v>68.23524457789915</v>
-      </c>
-      <c r="K10" t="n">
-        <v>514.4451765239781</v>
-      </c>
-      <c r="L10" t="n">
-        <v>104.5444039966898</v>
-      </c>
-      <c r="M10" t="n">
-        <v>503.9706026188204</v>
-      </c>
-      <c r="N10" t="n">
-        <v>97.85888320587904</v>
-      </c>
-      <c r="O10" t="n">
-        <v>508.1283955152184</v>
-      </c>
-      <c r="P10" t="n">
-        <v>89.37694738677193</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>509.8024035096637</v>
-      </c>
       <c r="R10" t="n">
-        <v>76.38733478707857</v>
+        <v>529.24</v>
       </c>
       <c r="S10" t="n">
-        <v>504.7861397230936</v>
+        <v>68.23999999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>73.8902792665785</v>
+        <v>514.45</v>
       </c>
       <c r="U10" t="n">
-        <v>501.9531910450396</v>
+        <v>104.54</v>
       </c>
       <c r="V10" t="n">
-        <v>77.2698467962045</v>
+        <v>503.97</v>
       </c>
       <c r="W10" t="n">
-        <v>502.7426238248793</v>
+        <v>97.86</v>
       </c>
       <c r="X10" t="n">
-        <v>81.20455922282612</v>
+        <v>508.13</v>
       </c>
       <c r="Y10" t="n">
-        <v>503.9956525636613</v>
+        <v>89.38</v>
       </c>
       <c r="Z10" t="n">
-        <v>83.6798028808262</v>
+        <v>509.8</v>
       </c>
       <c r="AA10" t="n">
+        <v>76.39</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>504.79</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>73.89</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>501.95</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>77.27</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>502.74</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>81.2</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>504</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>83.68000000000001</v>
+      </c>
+      <c r="AJ10" t="n">
         <v>0.4210526315789473</v>
       </c>
-      <c r="AB10" t="n">
+      <c r="AK10" t="n">
         <v>0.06896551724137931</v>
       </c>
-      <c r="AC10" t="n">
+      <c r="AL10" t="n">
         <v>-0.05128205128205128</v>
       </c>
-      <c r="AD10" t="n">
+      <c r="AM10" t="n">
         <v>-0.04081632653061224</v>
       </c>
-      <c r="AE10" t="n">
+      <c r="AN10" t="n">
         <v>-0.01694915254237288</v>
       </c>
-      <c r="AF10" t="n">
+      <c r="AO10" t="n">
         <v>-0.01449275362318841</v>
       </c>
-      <c r="AG10" t="n">
+      <c r="AP10" t="n">
         <v>-0.02531645569620253</v>
       </c>
-      <c r="AH10" t="n">
+      <c r="AQ10" t="n">
         <v>-0.03370786516853932</v>
       </c>
-      <c r="AI10" t="n">
+      <c r="AR10" t="n">
         <v>-0.0202020202020202</v>
       </c>
-      <c r="AJ10" t="n">
+      <c r="AS10" t="n">
         <v>542.075</v>
       </c>
-      <c r="AK10" t="n">
+      <c r="AT10" t="n">
         <v>521.1166666666667</v>
       </c>
-      <c r="AL10" t="n">
+      <c r="AU10" t="n">
         <v>509.7625</v>
       </c>
-      <c r="AM10" t="n">
+      <c r="AV10" t="n">
         <v>509.29</v>
       </c>
-      <c r="AN10" t="n">
+      <c r="AW10" t="n">
         <v>510.7166666666666</v>
       </c>
-      <c r="AO10" t="n">
+      <c r="AX10" t="n">
         <v>510.4285714285714</v>
       </c>
-      <c r="AP10" t="n">
+      <c r="AY10" t="n">
         <v>509.21875</v>
       </c>
-      <c r="AQ10" t="n">
+      <c r="AZ10" t="n">
         <v>507.5277777777778</v>
       </c>
-      <c r="AR10" t="n">
+      <c r="BA10" t="n">
         <v>508.12</v>
       </c>
-      <c r="AS10" t="n">
+      <c r="BB10" t="n">
         <v>54.20995641946228</v>
       </c>
-      <c r="AT10" t="n">
+      <c r="BC10" t="n">
         <v>65.27431645669596</v>
       </c>
-      <c r="AU10" t="n">
+      <c r="BD10" t="n">
         <v>73.90809220748429</v>
       </c>
-      <c r="AV10" t="n">
+      <c r="BE10" t="n">
         <v>78.82376481747113</v>
       </c>
-      <c r="AW10" t="n">
+      <c r="BF10" t="n">
         <v>79.70060469587975</v>
       </c>
-      <c r="AX10" t="n">
+      <c r="BG10" t="n">
         <v>77.89921536897558</v>
       </c>
-      <c r="AY10" t="n">
+      <c r="BH10" t="n">
         <v>76.7665024502061</v>
       </c>
-      <c r="AZ10" t="n">
+      <c r="BI10" t="n">
         <v>77.15514172796087</v>
       </c>
-      <c r="BA10" t="n">
+      <c r="BJ10" t="n">
         <v>78.38542976854818</v>
       </c>
-      <c r="BB10" t="n">
+      <c r="BK10" t="n">
         <v>404</v>
       </c>
-      <c r="BC10" t="n">
+      <c r="BL10" t="n">
         <v>404</v>
       </c>
-      <c r="BD10" t="n">
+      <c r="BM10" t="n">
         <v>404</v>
       </c>
-      <c r="BE10" t="n">
+      <c r="BN10" t="n">
         <v>401</v>
       </c>
-      <c r="BF10" t="n">
+      <c r="BO10" t="n">
         <v>401</v>
       </c>
-      <c r="BG10" t="n">
+      <c r="BP10" t="n">
         <v>401</v>
       </c>
-      <c r="BH10" t="n">
+      <c r="BQ10" t="n">
         <v>401</v>
       </c>
-      <c r="BI10" t="n">
+      <c r="BR10" t="n">
         <v>401</v>
       </c>
-      <c r="BJ10" t="n">
+      <c r="BS10" t="n">
         <v>401</v>
       </c>
-      <c r="BK10" t="n">
+      <c r="BT10" t="n">
         <v>632</v>
       </c>
-      <c r="BL10" t="n">
+      <c r="BU10" t="n">
         <v>632</v>
       </c>
-      <c r="BM10" t="n">
+      <c r="BV10" t="n">
         <v>632</v>
       </c>
-      <c r="BN10" t="n">
+      <c r="BW10" t="n">
         <v>632</v>
       </c>
-      <c r="BO10" t="n">
+      <c r="BX10" t="n">
         <v>632</v>
       </c>
-      <c r="BP10" t="n">
+      <c r="BY10" t="n">
         <v>632</v>
       </c>
-      <c r="BQ10" t="n">
+      <c r="BZ10" t="n">
         <v>632</v>
       </c>
-      <c r="BR10" t="n">
+      <c r="CA10" t="n">
         <v>632</v>
       </c>
-      <c r="BS10" t="n">
+      <c r="CB10" t="n">
         <v>632</v>
       </c>
-      <c r="BT10" t="n">
+      <c r="CC10" t="n">
         <v>0.8</v>
       </c>
-      <c r="BU10" t="n">
+      <c r="CD10" t="n">
         <v>0.8333333333333334</v>
       </c>
-      <c r="BV10" t="n">
+      <c r="CE10" t="n">
         <v>0.8181818181818182</v>
       </c>
-      <c r="BW10" t="n">
+      <c r="CF10" t="n">
         <v>0.4615384615384616</v>
       </c>
-      <c r="BX10" t="n">
+      <c r="CG10" t="n">
         <v>0.875</v>
       </c>
-      <c r="BY10" t="n">
+      <c r="CH10" t="n">
         <v>0.875</v>
       </c>
-      <c r="BZ10" t="n">
+      <c r="CI10" t="n">
         <v>1</v>
       </c>
-      <c r="CA10" t="n">
+      <c r="CJ10" t="n">
         <v>0.9</v>
       </c>
-      <c r="CB10" t="n">
+      <c r="CK10" t="n">
         <v>0.8333333333333334</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>504</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>83.68000000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S11_G6_498_60_ABS1</t>
+          <t>S10_G6_500_60_ABS1</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="C11" t="n">
+        <v>88.95478131949592</v>
+      </c>
+      <c r="D11" t="n">
         <v>60</v>
       </c>
-      <c r="D11" t="n">
-        <v>88.95478131949592</v>
-      </c>
       <c r="E11" t="n">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="F11" t="n">
         <v>200</v>
       </c>
       <c r="G11" t="n">
-        <v>0.485</v>
-      </c>
-      <c r="H11" t="inlineStr">
+        <v>77.5</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="Q11" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I11" t="n">
-        <v>505.6725311389164</v>
-      </c>
-      <c r="J11" t="n">
-        <v>41.56793495357648</v>
-      </c>
-      <c r="K11" t="n">
-        <v>508.1098392362993</v>
-      </c>
-      <c r="L11" t="n">
-        <v>64.74507711712235</v>
-      </c>
-      <c r="M11" t="n">
-        <v>502.8594460116189</v>
-      </c>
-      <c r="N11" t="n">
-        <v>84.21040817238965</v>
-      </c>
-      <c r="O11" t="n">
-        <v>499.9283520092086</v>
-      </c>
-      <c r="P11" t="n">
-        <v>79.25112669522115</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>506.1419336587875</v>
-      </c>
       <c r="R11" t="n">
-        <v>84.23439840681543</v>
+        <v>493.81</v>
       </c>
       <c r="S11" t="n">
-        <v>511.242392472025</v>
+        <v>73.78</v>
       </c>
       <c r="T11" t="n">
-        <v>79.9529534263925</v>
+        <v>483.41</v>
       </c>
       <c r="U11" t="n">
-        <v>508.7096220532412</v>
+        <v>67.17</v>
       </c>
       <c r="V11" t="n">
-        <v>81.56364254952715</v>
+        <v>495.62</v>
       </c>
       <c r="W11" t="n">
-        <v>511.4510944630569</v>
+        <v>60.85</v>
       </c>
       <c r="X11" t="n">
-        <v>78.28597140591701</v>
+        <v>500.36</v>
       </c>
       <c r="Y11" t="n">
-        <v>511.3230588372364</v>
+        <v>66.84</v>
       </c>
       <c r="Z11" t="n">
-        <v>77.51945942126028</v>
+        <v>498.21</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.1</v>
+        <v>70.22</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.03333333333333333</v>
+        <v>498.13</v>
       </c>
       <c r="AC11" t="n">
-        <v>-0.025</v>
+        <v>66.8</v>
       </c>
       <c r="AD11" t="n">
+        <v>494.37</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>62.08</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>495.59</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>66.43000000000001</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>495.52</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>65.40000000000001</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>-0.1333333333333333</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="AM11" t="n">
         <v>-0.04</v>
       </c>
-      <c r="AE11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>0.02857142857142857</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>0.01111111111111111</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>511.925</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>508.8833333333333</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>503.3125</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>500.3</v>
-      </c>
       <c r="AN11" t="n">
-        <v>503.1083333333333</v>
+        <v>-0.03333333333333333</v>
       </c>
       <c r="AO11" t="n">
-        <v>505.7428571428571</v>
+        <v>-0.05714285714285714</v>
       </c>
       <c r="AP11" t="n">
-        <v>505.9875</v>
+        <v>-0.05</v>
       </c>
       <c r="AQ11" t="n">
-        <v>505.4666666666666</v>
+        <v>-0.03333333333333333</v>
       </c>
       <c r="AR11" t="n">
-        <v>505.955</v>
+        <v>-0.03</v>
       </c>
       <c r="AS11" t="n">
-        <v>42.75709736406343</v>
+        <v>500.625</v>
       </c>
       <c r="AT11" t="n">
-        <v>54.15412931829135</v>
+        <v>489.0166666666667</v>
       </c>
       <c r="AU11" t="n">
-        <v>63.26207271145959</v>
+        <v>489.3625</v>
       </c>
       <c r="AV11" t="n">
-        <v>70.91170566274654</v>
+        <v>494.45</v>
       </c>
       <c r="AW11" t="n">
-        <v>73.74548526670783</v>
+        <v>495.675</v>
       </c>
       <c r="AX11" t="n">
-        <v>75.69878008344949</v>
+        <v>494.4214285714286</v>
       </c>
       <c r="AY11" t="n">
-        <v>77.31146321050973</v>
+        <v>494.8625</v>
       </c>
       <c r="AZ11" t="n">
-        <v>77.59906929567877</v>
+        <v>495.7555555555555</v>
       </c>
       <c r="BA11" t="n">
-        <v>77.4795648864912</v>
+        <v>495.66</v>
       </c>
       <c r="BB11" t="n">
-        <v>448</v>
+        <v>59.94442738904092</v>
       </c>
       <c r="BC11" t="n">
-        <v>411</v>
+        <v>66.55511291820903</v>
       </c>
       <c r="BD11" t="n">
-        <v>399</v>
+        <v>65.78416294025484</v>
       </c>
       <c r="BE11" t="n">
-        <v>388</v>
+        <v>65.9888437540771</v>
       </c>
       <c r="BF11" t="n">
-        <v>388</v>
+        <v>66.81443986893851</v>
       </c>
       <c r="BG11" t="n">
-        <v>388</v>
+        <v>66.64351515522645</v>
       </c>
       <c r="BH11" t="n">
-        <v>388</v>
+        <v>66.18378648694861</v>
       </c>
       <c r="BI11" t="n">
-        <v>388</v>
+        <v>65.5831636780713</v>
       </c>
       <c r="BJ11" t="n">
-        <v>388</v>
+        <v>65.12644931208824</v>
       </c>
       <c r="BK11" t="n">
-        <v>647</v>
+        <v>362</v>
       </c>
       <c r="BL11" t="n">
-        <v>647</v>
+        <v>362</v>
       </c>
       <c r="BM11" t="n">
-        <v>647</v>
+        <v>362</v>
       </c>
       <c r="BN11" t="n">
-        <v>647</v>
+        <v>362</v>
       </c>
       <c r="BO11" t="n">
-        <v>647</v>
+        <v>362</v>
       </c>
       <c r="BP11" t="n">
-        <v>647</v>
+        <v>362</v>
       </c>
       <c r="BQ11" t="n">
-        <v>647</v>
+        <v>362</v>
       </c>
       <c r="BR11" t="n">
-        <v>647</v>
+        <v>362</v>
       </c>
       <c r="BS11" t="n">
-        <v>647</v>
+        <v>362</v>
       </c>
       <c r="BT11" t="n">
-        <v>0.8333333333333334</v>
+        <v>594</v>
       </c>
       <c r="BU11" t="n">
-        <v>0.4444444444444444</v>
+        <v>594</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.7272727272727273</v>
+        <v>594</v>
       </c>
       <c r="BW11" t="n">
-        <v>0.6428571428571429</v>
+        <v>594</v>
       </c>
       <c r="BX11" t="n">
-        <v>0.7222222222222222</v>
+        <v>594</v>
       </c>
       <c r="BY11" t="n">
-        <v>0.7619047619047619</v>
+        <v>594</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0.7916666666666666</v>
+        <v>594</v>
       </c>
       <c r="CA11" t="n">
-        <v>0.8</v>
+        <v>594</v>
       </c>
       <c r="CB11" t="n">
-        <v>0.7352941176470589</v>
+        <v>594</v>
+      </c>
+      <c r="CC11" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD11" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="CE11" t="n">
+        <v>0.5555555555555556</v>
+      </c>
+      <c r="CF11" t="n">
+        <v>0.4545454545454545</v>
+      </c>
+      <c r="CG11" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="CH11" t="n">
+        <v>1</v>
+      </c>
+      <c r="CI11" t="n">
+        <v>0.2272727272727273</v>
+      </c>
+      <c r="CJ11" t="n">
+        <v>0.9642857142857143</v>
+      </c>
+      <c r="CK11" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL11" t="n">
+        <v>495.52</v>
+      </c>
+      <c r="CM11" t="n">
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S10_G6_500_60_ABS1</t>
+          <t>S11_G6_498_60_ABS1</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C12" t="n">
+        <v>88.95478131949592</v>
+      </c>
+      <c r="D12" t="n">
         <v>60</v>
       </c>
-      <c r="D12" t="n">
-        <v>88.95478131949592</v>
-      </c>
       <c r="E12" t="n">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="F12" t="n">
         <v>200</v>
       </c>
       <c r="G12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H12" t="inlineStr">
+        <v>77</v>
+      </c>
+      <c r="H12" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="L12" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="M12" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="P12" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="Q12" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I12" t="n">
-        <v>493.8116475638477</v>
-      </c>
-      <c r="J12" t="n">
-        <v>73.78268074075868</v>
-      </c>
-      <c r="K12" t="n">
-        <v>483.4143173786375</v>
-      </c>
-      <c r="L12" t="n">
-        <v>67.17143539530355</v>
-      </c>
-      <c r="M12" t="n">
-        <v>495.6185896565656</v>
-      </c>
-      <c r="N12" t="n">
-        <v>60.85119069729429</v>
-      </c>
-      <c r="O12" t="n">
-        <v>500.361113661188</v>
-      </c>
-      <c r="P12" t="n">
-        <v>66.84280681178986</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>498.2125366558886</v>
-      </c>
       <c r="R12" t="n">
-        <v>70.2164807705222</v>
+        <v>505.67</v>
       </c>
       <c r="S12" t="n">
-        <v>498.1298648476818</v>
+        <v>41.57</v>
       </c>
       <c r="T12" t="n">
-        <v>66.80282665882211</v>
+        <v>508.11</v>
       </c>
       <c r="U12" t="n">
-        <v>494.3711716870891</v>
+        <v>64.75</v>
       </c>
       <c r="V12" t="n">
-        <v>62.07961383766249</v>
+        <v>502.86</v>
       </c>
       <c r="W12" t="n">
-        <v>495.5947677095461</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="X12" t="n">
-        <v>66.43108271615114</v>
+        <v>499.93</v>
       </c>
       <c r="Y12" t="n">
-        <v>495.5152664921258</v>
+        <v>79.25</v>
       </c>
       <c r="Z12" t="n">
-        <v>65.39975348218472</v>
+        <v>506.14</v>
       </c>
       <c r="AA12" t="n">
-        <v>-0.05</v>
+        <v>84.23</v>
       </c>
       <c r="AB12" t="n">
-        <v>-0.1333333333333333</v>
+        <v>511.24</v>
       </c>
       <c r="AC12" t="n">
-        <v>-0.1</v>
+        <v>79.95</v>
       </c>
       <c r="AD12" t="n">
+        <v>508.71</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>81.56</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>511.45</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>78.29000000000001</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>511.32</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>77.52</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0.03333333333333333</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>-0.025</v>
+      </c>
+      <c r="AM12" t="n">
         <v>-0.04</v>
       </c>
-      <c r="AE12" t="n">
-        <v>-0.03333333333333333</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>-0.05714285714285714</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>-0.03333333333333333</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>500.625</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>489.0166666666667</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>489.3625</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>494.45</v>
-      </c>
       <c r="AN12" t="n">
-        <v>495.675</v>
+        <v>0</v>
       </c>
       <c r="AO12" t="n">
-        <v>494.4214285714286</v>
+        <v>0.02857142857142857</v>
       </c>
       <c r="AP12" t="n">
-        <v>494.8625</v>
+        <v>0.025</v>
       </c>
       <c r="AQ12" t="n">
-        <v>495.7555555555555</v>
+        <v>0.01111111111111111</v>
       </c>
       <c r="AR12" t="n">
-        <v>495.66</v>
+        <v>0.01</v>
       </c>
       <c r="AS12" t="n">
-        <v>59.94442738904092</v>
+        <v>511.925</v>
       </c>
       <c r="AT12" t="n">
-        <v>66.55511291820903</v>
+        <v>508.8833333333333</v>
       </c>
       <c r="AU12" t="n">
-        <v>65.78416294025484</v>
+        <v>503.3125</v>
       </c>
       <c r="AV12" t="n">
-        <v>65.9888437540771</v>
+        <v>500.3</v>
       </c>
       <c r="AW12" t="n">
-        <v>66.81443986893851</v>
+        <v>503.1083333333333</v>
       </c>
       <c r="AX12" t="n">
-        <v>66.64351515522645</v>
+        <v>505.7428571428571</v>
       </c>
       <c r="AY12" t="n">
-        <v>66.18378648694861</v>
+        <v>505.9875</v>
       </c>
       <c r="AZ12" t="n">
-        <v>65.5831636780713</v>
+        <v>505.4666666666666</v>
       </c>
       <c r="BA12" t="n">
-        <v>65.12644931208824</v>
+        <v>505.955</v>
       </c>
       <c r="BB12" t="n">
-        <v>362</v>
+        <v>42.75709736406343</v>
       </c>
       <c r="BC12" t="n">
-        <v>362</v>
+        <v>54.15412931829135</v>
       </c>
       <c r="BD12" t="n">
-        <v>362</v>
+        <v>63.26207271145959</v>
       </c>
       <c r="BE12" t="n">
-        <v>362</v>
+        <v>70.91170566274654</v>
       </c>
       <c r="BF12" t="n">
-        <v>362</v>
+        <v>73.74548526670783</v>
       </c>
       <c r="BG12" t="n">
-        <v>362</v>
+        <v>75.69878008344949</v>
       </c>
       <c r="BH12" t="n">
-        <v>362</v>
+        <v>77.31146321050973</v>
       </c>
       <c r="BI12" t="n">
-        <v>362</v>
+        <v>77.59906929567877</v>
       </c>
       <c r="BJ12" t="n">
-        <v>362</v>
+        <v>77.4795648864912</v>
       </c>
       <c r="BK12" t="n">
-        <v>594</v>
+        <v>448</v>
       </c>
       <c r="BL12" t="n">
-        <v>594</v>
+        <v>411</v>
       </c>
       <c r="BM12" t="n">
-        <v>594</v>
+        <v>399</v>
       </c>
       <c r="BN12" t="n">
-        <v>594</v>
+        <v>388</v>
       </c>
       <c r="BO12" t="n">
-        <v>594</v>
+        <v>388</v>
       </c>
       <c r="BP12" t="n">
-        <v>594</v>
+        <v>388</v>
       </c>
       <c r="BQ12" t="n">
-        <v>594</v>
+        <v>388</v>
       </c>
       <c r="BR12" t="n">
-        <v>594</v>
+        <v>388</v>
       </c>
       <c r="BS12" t="n">
-        <v>594</v>
+        <v>388</v>
       </c>
       <c r="BT12" t="n">
-        <v>1</v>
+        <v>647</v>
       </c>
       <c r="BU12" t="n">
-        <v>0.625</v>
+        <v>647</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.5555555555555556</v>
+        <v>647</v>
       </c>
       <c r="BW12" t="n">
-        <v>0.4545454545454545</v>
+        <v>647</v>
       </c>
       <c r="BX12" t="n">
-        <v>0.9375</v>
+        <v>647</v>
       </c>
       <c r="BY12" t="n">
-        <v>1</v>
+        <v>647</v>
       </c>
       <c r="BZ12" t="n">
-        <v>0.2272727272727273</v>
+        <v>647</v>
       </c>
       <c r="CA12" t="n">
-        <v>0.9642857142857143</v>
+        <v>647</v>
       </c>
       <c r="CB12" t="n">
-        <v>1</v>
+        <v>647</v>
+      </c>
+      <c r="CC12" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="CD12" t="n">
+        <v>0.4444444444444444</v>
+      </c>
+      <c r="CE12" t="n">
+        <v>0.7272727272727273</v>
+      </c>
+      <c r="CF12" t="n">
+        <v>0.6428571428571429</v>
+      </c>
+      <c r="CG12" t="n">
+        <v>0.7222222222222222</v>
+      </c>
+      <c r="CH12" t="n">
+        <v>0.7619047619047619</v>
+      </c>
+      <c r="CI12" t="n">
+        <v>0.7916666666666666</v>
+      </c>
+      <c r="CJ12" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="CK12" t="n">
+        <v>0.7352941176470589</v>
+      </c>
+      <c r="CL12" t="n">
+        <v>511.32</v>
+      </c>
+      <c r="CM12" t="n">
+        <v>77.52</v>
       </c>
     </row>
     <row r="13">
@@ -3546,10 +3964,10 @@
         <v>498</v>
       </c>
       <c r="C13" t="n">
+        <v>88.95478131949592</v>
+      </c>
+      <c r="D13" t="n">
         <v>60</v>
-      </c>
-      <c r="D13" t="n">
-        <v>88.95478131949592</v>
       </c>
       <c r="E13" t="n">
         <v>498</v>
@@ -3558,244 +3976,277 @@
         <v>200</v>
       </c>
       <c r="G13" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H13" t="inlineStr">
+        <v>76</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="L13" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="M13" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="O13" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="Q13" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I13" t="n">
-        <v>488.4888759313627</v>
-      </c>
-      <c r="J13" t="n">
-        <v>83.1203690838861</v>
-      </c>
-      <c r="K13" t="n">
-        <v>489.3284931624362</v>
-      </c>
-      <c r="L13" t="n">
-        <v>64.00372468728204</v>
-      </c>
-      <c r="M13" t="n">
-        <v>483.1076579376166</v>
-      </c>
-      <c r="N13" t="n">
-        <v>67.45319168445397</v>
-      </c>
-      <c r="O13" t="n">
-        <v>488.9201733101154</v>
-      </c>
-      <c r="P13" t="n">
-        <v>61.68973035434968</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>481.5036476432546</v>
-      </c>
       <c r="R13" t="n">
-        <v>64.66766346259139</v>
+        <v>488.49</v>
       </c>
       <c r="S13" t="n">
-        <v>485.3680232527259</v>
+        <v>83.12</v>
       </c>
       <c r="T13" t="n">
-        <v>64.67543968366442</v>
+        <v>489.33</v>
       </c>
       <c r="U13" t="n">
-        <v>489.4300669479001</v>
+        <v>64</v>
       </c>
       <c r="V13" t="n">
-        <v>68.61816379100489</v>
+        <v>483.11</v>
       </c>
       <c r="W13" t="n">
-        <v>489.2234348639933</v>
+        <v>67.45</v>
       </c>
       <c r="X13" t="n">
-        <v>67.8936721940847</v>
+        <v>488.92</v>
       </c>
       <c r="Y13" t="n">
-        <v>488.5750098550963</v>
+        <v>61.69</v>
       </c>
       <c r="Z13" t="n">
-        <v>65.19392164504899</v>
+        <v>481.5</v>
       </c>
       <c r="AA13" t="n">
+        <v>64.67</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>485.37</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>64.68000000000001</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>489.43</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>68.62</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>489.22</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>67.89</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>488.58</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>65.19</v>
+      </c>
+      <c r="AJ13" t="n">
         <v>-0.4</v>
       </c>
-      <c r="AB13" t="n">
+      <c r="AK13" t="n">
         <v>-0.1</v>
       </c>
-      <c r="AC13" t="n">
+      <c r="AL13" t="n">
         <v>-0.125</v>
       </c>
-      <c r="AD13" t="n">
+      <c r="AM13" t="n">
         <v>-0.06</v>
       </c>
-      <c r="AE13" t="n">
+      <c r="AN13" t="n">
         <v>-0.06666666666666667</v>
       </c>
-      <c r="AF13" t="n">
+      <c r="AO13" t="n">
         <v>-0.04285714285714286</v>
       </c>
-      <c r="AG13" t="n">
+      <c r="AP13" t="n">
         <v>-0.0375</v>
       </c>
-      <c r="AH13" t="n">
+      <c r="AQ13" t="n">
         <v>-0.03333333333333333</v>
       </c>
-      <c r="AI13" t="n">
+      <c r="AR13" t="n">
         <v>-0.04</v>
       </c>
-      <c r="AJ13" t="n">
+      <c r="AS13" t="n">
         <v>481.725</v>
       </c>
-      <c r="AK13" t="n">
+      <c r="AT13" t="n">
         <v>497.45</v>
       </c>
-      <c r="AL13" t="n">
+      <c r="AU13" t="n">
         <v>489.9375</v>
       </c>
-      <c r="AM13" t="n">
+      <c r="AV13" t="n">
         <v>490.65</v>
       </c>
-      <c r="AN13" t="n">
+      <c r="AW13" t="n">
         <v>488.075</v>
       </c>
-      <c r="AO13" t="n">
+      <c r="AX13" t="n">
         <v>488.7214285714286</v>
       </c>
-      <c r="AP13" t="n">
+      <c r="AY13" t="n">
         <v>488.875</v>
       </c>
-      <c r="AQ13" t="n">
+      <c r="AZ13" t="n">
         <v>488.7166666666666</v>
       </c>
-      <c r="AR13" t="n">
+      <c r="BA13" t="n">
         <v>488.275</v>
       </c>
-      <c r="AS13" t="n">
+      <c r="BB13" t="n">
         <v>49.22651089606088</v>
       </c>
-      <c r="AT13" t="n">
+      <c r="BC13" t="n">
         <v>62.18960926071171</v>
       </c>
-      <c r="AU13" t="n">
+      <c r="BD13" t="n">
         <v>66.32332616621396</v>
       </c>
-      <c r="AV13" t="n">
+      <c r="BE13" t="n">
         <v>65.48242130526329</v>
       </c>
-      <c r="AW13" t="n">
+      <c r="BF13" t="n">
         <v>64.96116307712889</v>
       </c>
-      <c r="AX13" t="n">
+      <c r="BG13" t="n">
         <v>65.04746265581143</v>
       </c>
-      <c r="AY13" t="n">
+      <c r="BH13" t="n">
         <v>64.67744487068116</v>
       </c>
-      <c r="AZ13" t="n">
+      <c r="BI13" t="n">
         <v>65.42512896433603</v>
       </c>
-      <c r="BA13" t="n">
+      <c r="BJ13" t="n">
         <v>65.25549306380269</v>
       </c>
-      <c r="BB13" t="n">
+      <c r="BK13" t="n">
         <v>345</v>
       </c>
-      <c r="BC13" t="n">
+      <c r="BL13" t="n">
         <v>345</v>
       </c>
-      <c r="BD13" t="n">
+      <c r="BM13" t="n">
         <v>345</v>
       </c>
-      <c r="BE13" t="n">
+      <c r="BN13" t="n">
         <v>345</v>
       </c>
-      <c r="BF13" t="n">
+      <c r="BO13" t="n">
         <v>345</v>
       </c>
-      <c r="BG13" t="n">
+      <c r="BP13" t="n">
         <v>345</v>
       </c>
-      <c r="BH13" t="n">
+      <c r="BQ13" t="n">
         <v>345</v>
       </c>
-      <c r="BI13" t="n">
+      <c r="BR13" t="n">
         <v>345</v>
       </c>
-      <c r="BJ13" t="n">
+      <c r="BS13" t="n">
         <v>345</v>
       </c>
-      <c r="BK13" t="n">
+      <c r="BT13" t="n">
         <v>574</v>
       </c>
-      <c r="BL13" t="n">
+      <c r="BU13" t="n">
         <v>585</v>
       </c>
-      <c r="BM13" t="n">
+      <c r="BV13" t="n">
         <v>585</v>
       </c>
-      <c r="BN13" t="n">
+      <c r="BW13" t="n">
         <v>585</v>
       </c>
-      <c r="BO13" t="n">
+      <c r="BX13" t="n">
         <v>585</v>
       </c>
-      <c r="BP13" t="n">
+      <c r="BY13" t="n">
         <v>585</v>
       </c>
-      <c r="BQ13" t="n">
+      <c r="BZ13" t="n">
         <v>585</v>
       </c>
-      <c r="BR13" t="n">
+      <c r="CA13" t="n">
         <v>585</v>
       </c>
-      <c r="BS13" t="n">
+      <c r="CB13" t="n">
         <v>585</v>
       </c>
-      <c r="BT13" t="n">
+      <c r="CC13" t="n">
         <v>0.8571428571428571</v>
       </c>
-      <c r="BU13" t="n">
+      <c r="CD13" t="n">
         <v>1</v>
       </c>
-      <c r="BV13" t="n">
+      <c r="CE13" t="n">
         <v>0.7272727272727273</v>
       </c>
-      <c r="BW13" t="n">
+      <c r="CF13" t="n">
         <v>0.4166666666666667</v>
       </c>
-      <c r="BX13" t="n">
+      <c r="CG13" t="n">
         <v>0.7647058823529411</v>
       </c>
-      <c r="BY13" t="n">
+      <c r="CH13" t="n">
         <v>0.8571428571428571</v>
       </c>
-      <c r="BZ13" t="n">
+      <c r="CI13" t="n">
         <v>1</v>
       </c>
-      <c r="CA13" t="n">
+      <c r="CJ13" t="n">
         <v>0.9310344827586207</v>
       </c>
-      <c r="CB13" t="n">
+      <c r="CK13" t="n">
         <v>0.9117647058823529</v>
+      </c>
+      <c r="CL13" t="n">
+        <v>488.58</v>
+      </c>
+      <c r="CM13" t="n">
+        <v>65.19</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S14_G6_498_62_ABS1</t>
+          <t>S13_G6_498_62_ABS1</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>498</v>
       </c>
       <c r="C14" t="n">
+        <v>91.91994069681246</v>
+      </c>
+      <c r="D14" t="n">
         <v>62</v>
-      </c>
-      <c r="D14" t="n">
-        <v>91.91994069681246</v>
       </c>
       <c r="E14" t="n">
         <v>498</v>
@@ -3804,244 +4255,277 @@
         <v>200</v>
       </c>
       <c r="G14" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="H14" t="inlineStr">
+        <v>73</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="L14" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="M14" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Q14" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I14" t="n">
-        <v>531.5791373995253</v>
-      </c>
-      <c r="J14" t="n">
-        <v>61.61159921641896</v>
-      </c>
-      <c r="K14" t="n">
-        <v>525.8540125009496</v>
-      </c>
-      <c r="L14" t="n">
-        <v>68.57230168566554</v>
-      </c>
-      <c r="M14" t="n">
-        <v>522.862792944028</v>
-      </c>
-      <c r="N14" t="n">
-        <v>74.02249758256109</v>
-      </c>
-      <c r="O14" t="n">
-        <v>516.5273331876804</v>
-      </c>
-      <c r="P14" t="n">
-        <v>73.07939088826204</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>518.3745225859352</v>
-      </c>
       <c r="R14" t="n">
-        <v>68.18569416197303</v>
+        <v>473.4</v>
       </c>
       <c r="S14" t="n">
-        <v>516.2380072686901</v>
+        <v>46.93</v>
       </c>
       <c r="T14" t="n">
-        <v>64.64776857070599</v>
+        <v>472.65</v>
       </c>
       <c r="U14" t="n">
-        <v>515.9786997552186</v>
+        <v>42.05</v>
       </c>
       <c r="V14" t="n">
-        <v>66.03161963385682</v>
+        <v>471.21</v>
       </c>
       <c r="W14" t="n">
-        <v>516.274215818721</v>
+        <v>49.03</v>
       </c>
       <c r="X14" t="n">
-        <v>67.63762684660105</v>
+        <v>468.62</v>
       </c>
       <c r="Y14" t="n">
-        <v>513.9019214738959</v>
+        <v>51.23</v>
       </c>
       <c r="Z14" t="n">
-        <v>62.45987501492949</v>
+        <v>471.33</v>
       </c>
       <c r="AA14" t="n">
+        <v>60.92</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>472.92</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>64.25</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>476.59</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>69.20999999999999</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>479.2</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>69.77</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>485.04</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>72.25</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>-0.3846153846153846</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>-0.2068965517241379</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>-0.2051282051282051</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>-0.1836734693877551</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>-0.1186440677966102</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>-0.1014492753623188</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>-0.05063291139240506</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>-0.03370786516853932</v>
+      </c>
+      <c r="AR14" t="n">
         <v>0</v>
       </c>
-      <c r="AB14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>-0.025</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>-0.03333333333333333</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>-0.02857142857142857</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>-0.025</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>-0.02222222222222222</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>515.2</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>519.7833333333333</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>518.4875</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>516.51</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>515.85</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>516.3071428571428</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>516.05625</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>516.3111111111111</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>516.675</v>
-      </c>
       <c r="AS14" t="n">
-        <v>69.88139952805753</v>
+        <v>481.175</v>
       </c>
       <c r="AT14" t="n">
-        <v>68.56507654937916</v>
+        <v>479.9166666666667</v>
       </c>
       <c r="AU14" t="n">
-        <v>71.54211936859294</v>
+        <v>474.9625</v>
       </c>
       <c r="AV14" t="n">
-        <v>73.39570764016108</v>
+        <v>471.85</v>
       </c>
       <c r="AW14" t="n">
-        <v>72.26694149701738</v>
+        <v>473.7416666666667</v>
       </c>
       <c r="AX14" t="n">
-        <v>70.38870611809534</v>
+        <v>473.1571428571428</v>
       </c>
       <c r="AY14" t="n">
-        <v>69.00699664481495</v>
+        <v>476.54375</v>
       </c>
       <c r="AZ14" t="n">
-        <v>68.26201879432327</v>
+        <v>477.4444444444445</v>
       </c>
       <c r="BA14" t="n">
-        <v>67.45546215837528</v>
+        <v>480.145</v>
       </c>
       <c r="BB14" t="n">
-        <v>347</v>
+        <v>52.30290981389085</v>
       </c>
       <c r="BC14" t="n">
-        <v>347</v>
+        <v>52.36292952928521</v>
       </c>
       <c r="BD14" t="n">
-        <v>347</v>
+        <v>53.16987957246095</v>
       </c>
       <c r="BE14" t="n">
-        <v>347</v>
+        <v>53.43058581000211</v>
       </c>
       <c r="BF14" t="n">
-        <v>347</v>
+        <v>56.09315107232096</v>
       </c>
       <c r="BG14" t="n">
-        <v>347</v>
+        <v>57.86280219234997</v>
       </c>
       <c r="BH14" t="n">
-        <v>347</v>
+        <v>61.22906242902548</v>
       </c>
       <c r="BI14" t="n">
-        <v>347</v>
+        <v>63.86611188191732</v>
       </c>
       <c r="BJ14" t="n">
-        <v>347</v>
+        <v>65.35972747036206</v>
       </c>
       <c r="BK14" t="n">
-        <v>609</v>
+        <v>404</v>
       </c>
       <c r="BL14" t="n">
-        <v>615</v>
+        <v>404</v>
       </c>
       <c r="BM14" t="n">
-        <v>622</v>
+        <v>400</v>
       </c>
       <c r="BN14" t="n">
-        <v>622</v>
+        <v>399</v>
       </c>
       <c r="BO14" t="n">
-        <v>622</v>
+        <v>385</v>
       </c>
       <c r="BP14" t="n">
-        <v>622</v>
+        <v>385</v>
       </c>
       <c r="BQ14" t="n">
-        <v>622</v>
+        <v>385</v>
       </c>
       <c r="BR14" t="n">
-        <v>622</v>
+        <v>381</v>
       </c>
       <c r="BS14" t="n">
-        <v>622</v>
+        <v>381</v>
       </c>
       <c r="BT14" t="n">
-        <v>0.8571428571428571</v>
+        <v>656</v>
       </c>
       <c r="BU14" t="n">
-        <v>0.8</v>
+        <v>656</v>
       </c>
       <c r="BV14" t="n">
-        <v>0.7692307692307693</v>
+        <v>656</v>
       </c>
       <c r="BW14" t="n">
-        <v>0.5555555555555556</v>
+        <v>656</v>
       </c>
       <c r="BX14" t="n">
-        <v>0.6363636363636364</v>
+        <v>656</v>
       </c>
       <c r="BY14" t="n">
+        <v>656</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>656</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>656</v>
+      </c>
+      <c r="CB14" t="n">
+        <v>656</v>
+      </c>
+      <c r="CC14" t="n">
         <v>0.625</v>
       </c>
-      <c r="BZ14" t="n">
-        <v>0.7692307692307693</v>
-      </c>
-      <c r="CA14" t="n">
-        <v>0.8571428571428571</v>
-      </c>
-      <c r="CB14" t="n">
-        <v>0.9032258064516129</v>
+      <c r="CD14" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="CE14" t="n">
+        <v>0.5454545454545454</v>
+      </c>
+      <c r="CF14" t="n">
+        <v>0.3529411764705883</v>
+      </c>
+      <c r="CG14" t="n">
+        <v>1</v>
+      </c>
+      <c r="CH14" t="n">
+        <v>0.9615384615384616</v>
+      </c>
+      <c r="CI14" t="n">
+        <v>0.9285714285714286</v>
+      </c>
+      <c r="CJ14" t="n">
+        <v>0.9615384615384616</v>
+      </c>
+      <c r="CK14" t="n">
+        <v>0.9655172413793104</v>
+      </c>
+      <c r="CL14" t="n">
+        <v>485.04</v>
+      </c>
+      <c r="CM14" t="n">
+        <v>72.25</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S13_G6_498_62_ABS1</t>
+          <t>S14_G6_498_62_ABS1</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>498</v>
       </c>
       <c r="C15" t="n">
+        <v>91.91994069681246</v>
+      </c>
+      <c r="D15" t="n">
         <v>62</v>
-      </c>
-      <c r="D15" t="n">
-        <v>91.91994069681246</v>
       </c>
       <c r="E15" t="n">
         <v>498</v>
@@ -4050,228 +4534,261 @@
         <v>200</v>
       </c>
       <c r="G15" t="n">
-        <v>0.485</v>
-      </c>
-      <c r="H15" t="inlineStr">
+        <v>77.5</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="L15" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="M15" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="O15" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="Q15" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I15" t="n">
-        <v>473.4009413436704</v>
-      </c>
-      <c r="J15" t="n">
-        <v>46.92701652936075</v>
-      </c>
-      <c r="K15" t="n">
-        <v>472.650013903131</v>
-      </c>
-      <c r="L15" t="n">
-        <v>42.0465868312391</v>
-      </c>
-      <c r="M15" t="n">
-        <v>471.2093920383044</v>
-      </c>
-      <c r="N15" t="n">
-        <v>49.02575033680055</v>
-      </c>
-      <c r="O15" t="n">
-        <v>468.6152796463405</v>
-      </c>
-      <c r="P15" t="n">
-        <v>51.2269482733337</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>471.3306030372084</v>
-      </c>
       <c r="R15" t="n">
-        <v>60.91719067605431</v>
+        <v>531.58</v>
       </c>
       <c r="S15" t="n">
-        <v>472.9215646155882</v>
+        <v>61.61</v>
       </c>
       <c r="T15" t="n">
-        <v>64.25375666602156</v>
+        <v>525.85</v>
       </c>
       <c r="U15" t="n">
-        <v>476.5910105323878</v>
+        <v>68.56999999999999</v>
       </c>
       <c r="V15" t="n">
-        <v>69.20998127356178</v>
+        <v>522.86</v>
       </c>
       <c r="W15" t="n">
-        <v>479.1996901255262</v>
+        <v>74.02</v>
       </c>
       <c r="X15" t="n">
-        <v>69.76811899119215</v>
+        <v>516.53</v>
       </c>
       <c r="Y15" t="n">
-        <v>485.0373756721511</v>
+        <v>73.08</v>
       </c>
       <c r="Z15" t="n">
-        <v>72.24922427855641</v>
+        <v>518.37</v>
       </c>
       <c r="AA15" t="n">
-        <v>-0.3846153846153846</v>
+        <v>68.19</v>
       </c>
       <c r="AB15" t="n">
-        <v>-0.2068965517241379</v>
+        <v>516.24</v>
       </c>
       <c r="AC15" t="n">
-        <v>-0.2051282051282051</v>
+        <v>64.65000000000001</v>
       </c>
       <c r="AD15" t="n">
-        <v>-0.1836734693877551</v>
+        <v>515.98</v>
       </c>
       <c r="AE15" t="n">
-        <v>-0.1186440677966102</v>
+        <v>66.03</v>
       </c>
       <c r="AF15" t="n">
-        <v>-0.1014492753623188</v>
+        <v>516.27</v>
       </c>
       <c r="AG15" t="n">
-        <v>-0.05063291139240506</v>
+        <v>67.64</v>
       </c>
       <c r="AH15" t="n">
-        <v>-0.03370786516853932</v>
+        <v>513.9</v>
       </c>
       <c r="AI15" t="n">
+        <v>62.46</v>
+      </c>
+      <c r="AJ15" t="n">
         <v>0</v>
       </c>
-      <c r="AJ15" t="n">
-        <v>481.175</v>
-      </c>
       <c r="AK15" t="n">
-        <v>479.9166666666667</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
-        <v>474.9625</v>
+        <v>-0.025</v>
       </c>
       <c r="AM15" t="n">
-        <v>471.85</v>
+        <v>-0.04</v>
       </c>
       <c r="AN15" t="n">
-        <v>473.7416666666667</v>
+        <v>-0.03333333333333333</v>
       </c>
       <c r="AO15" t="n">
-        <v>473.1571428571428</v>
+        <v>-0.02857142857142857</v>
       </c>
       <c r="AP15" t="n">
-        <v>476.54375</v>
+        <v>-0.025</v>
       </c>
       <c r="AQ15" t="n">
-        <v>477.4444444444445</v>
+        <v>-0.02222222222222222</v>
       </c>
       <c r="AR15" t="n">
-        <v>480.145</v>
+        <v>-0.01</v>
       </c>
       <c r="AS15" t="n">
-        <v>52.30290981389085</v>
+        <v>515.2</v>
       </c>
       <c r="AT15" t="n">
-        <v>52.36292952928521</v>
+        <v>519.7833333333333</v>
       </c>
       <c r="AU15" t="n">
-        <v>53.16987957246095</v>
+        <v>518.4875</v>
       </c>
       <c r="AV15" t="n">
-        <v>53.43058581000211</v>
+        <v>516.51</v>
       </c>
       <c r="AW15" t="n">
-        <v>56.09315107232096</v>
+        <v>515.85</v>
       </c>
       <c r="AX15" t="n">
-        <v>57.86280219234997</v>
+        <v>516.3071428571428</v>
       </c>
       <c r="AY15" t="n">
-        <v>61.22906242902548</v>
+        <v>516.05625</v>
       </c>
       <c r="AZ15" t="n">
-        <v>63.86611188191732</v>
+        <v>516.3111111111111</v>
       </c>
       <c r="BA15" t="n">
-        <v>65.35972747036206</v>
+        <v>516.675</v>
       </c>
       <c r="BB15" t="n">
-        <v>404</v>
+        <v>69.88139952805753</v>
       </c>
       <c r="BC15" t="n">
-        <v>404</v>
+        <v>68.56507654937916</v>
       </c>
       <c r="BD15" t="n">
-        <v>400</v>
+        <v>71.54211936859294</v>
       </c>
       <c r="BE15" t="n">
-        <v>399</v>
+        <v>73.39570764016108</v>
       </c>
       <c r="BF15" t="n">
-        <v>385</v>
+        <v>72.26694149701738</v>
       </c>
       <c r="BG15" t="n">
-        <v>385</v>
+        <v>70.38870611809534</v>
       </c>
       <c r="BH15" t="n">
-        <v>385</v>
+        <v>69.00699664481495</v>
       </c>
       <c r="BI15" t="n">
-        <v>381</v>
+        <v>68.26201879432327</v>
       </c>
       <c r="BJ15" t="n">
-        <v>381</v>
+        <v>67.45546215837528</v>
       </c>
       <c r="BK15" t="n">
-        <v>656</v>
+        <v>347</v>
       </c>
       <c r="BL15" t="n">
-        <v>656</v>
+        <v>347</v>
       </c>
       <c r="BM15" t="n">
-        <v>656</v>
+        <v>347</v>
       </c>
       <c r="BN15" t="n">
-        <v>656</v>
+        <v>347</v>
       </c>
       <c r="BO15" t="n">
-        <v>656</v>
+        <v>347</v>
       </c>
       <c r="BP15" t="n">
-        <v>656</v>
+        <v>347</v>
       </c>
       <c r="BQ15" t="n">
-        <v>656</v>
+        <v>347</v>
       </c>
       <c r="BR15" t="n">
-        <v>656</v>
+        <v>347</v>
       </c>
       <c r="BS15" t="n">
-        <v>656</v>
+        <v>347</v>
       </c>
       <c r="BT15" t="n">
+        <v>609</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>615</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>622</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>622</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>622</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>622</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>622</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>622</v>
+      </c>
+      <c r="CB15" t="n">
+        <v>622</v>
+      </c>
+      <c r="CC15" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="CD15" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="CE15" t="n">
+        <v>0.7692307692307693</v>
+      </c>
+      <c r="CF15" t="n">
+        <v>0.5555555555555556</v>
+      </c>
+      <c r="CG15" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="CH15" t="n">
         <v>0.625</v>
       </c>
-      <c r="BU15" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="BV15" t="n">
-        <v>0.5454545454545454</v>
-      </c>
-      <c r="BW15" t="n">
-        <v>0.3529411764705883</v>
-      </c>
-      <c r="BX15" t="n">
-        <v>1</v>
-      </c>
-      <c r="BY15" t="n">
-        <v>0.9615384615384616</v>
-      </c>
-      <c r="BZ15" t="n">
-        <v>0.9285714285714286</v>
-      </c>
-      <c r="CA15" t="n">
-        <v>0.9615384615384616</v>
-      </c>
-      <c r="CB15" t="n">
-        <v>0.9655172413793104</v>
+      <c r="CI15" t="n">
+        <v>0.7692307692307693</v>
+      </c>
+      <c r="CJ15" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="CK15" t="n">
+        <v>0.9032258064516129</v>
+      </c>
+      <c r="CL15" t="n">
+        <v>513.9</v>
+      </c>
+      <c r="CM15" t="n">
+        <v>62.46</v>
       </c>
     </row>
     <row r="16">
@@ -4284,10 +4801,10 @@
         <v>502</v>
       </c>
       <c r="C16" t="n">
+        <v>90.43736100815418</v>
+      </c>
+      <c r="D16" t="n">
         <v>61</v>
-      </c>
-      <c r="D16" t="n">
-        <v>90.43736100815418</v>
       </c>
       <c r="E16" t="n">
         <v>502</v>
@@ -4296,966 +4813,1098 @@
         <v>200</v>
       </c>
       <c r="G16" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="H16" t="inlineStr">
+        <v>72</v>
+      </c>
+      <c r="H16" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="I16" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="L16" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="M16" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="P16" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="Q16" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I16" t="n">
-        <v>542.2124172620494</v>
-      </c>
-      <c r="J16" t="n">
-        <v>38.00359499729058</v>
-      </c>
-      <c r="K16" t="n">
-        <v>522.9249158331519</v>
-      </c>
-      <c r="L16" t="n">
-        <v>93.95450272673976</v>
-      </c>
-      <c r="M16" t="n">
-        <v>523.158475603575</v>
-      </c>
-      <c r="N16" t="n">
-        <v>71.22930943437036</v>
-      </c>
-      <c r="O16" t="n">
-        <v>523.8190622748474</v>
-      </c>
-      <c r="P16" t="n">
-        <v>74.94353952136382</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>528.0778060003356</v>
-      </c>
       <c r="R16" t="n">
-        <v>77.22440950729157</v>
+        <v>542.21</v>
       </c>
       <c r="S16" t="n">
-        <v>527.9907167653245</v>
+        <v>38</v>
       </c>
       <c r="T16" t="n">
-        <v>76.54578836163471</v>
+        <v>522.92</v>
       </c>
       <c r="U16" t="n">
-        <v>528.8044381981023</v>
+        <v>93.95</v>
       </c>
       <c r="V16" t="n">
-        <v>75.9631843486697</v>
+        <v>523.16</v>
       </c>
       <c r="W16" t="n">
-        <v>517.8622365948978</v>
+        <v>71.23</v>
       </c>
       <c r="X16" t="n">
-        <v>91.43662542103358</v>
+        <v>523.8200000000001</v>
       </c>
       <c r="Y16" t="n">
-        <v>515.449843024433</v>
+        <v>74.94</v>
       </c>
       <c r="Z16" t="n">
-        <v>86.20062456576113</v>
+        <v>528.08</v>
       </c>
       <c r="AA16" t="n">
+        <v>77.22</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>527.99</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>76.55</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>528.8</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>75.95999999999999</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>517.86</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>91.44</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>515.45</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>86.2</v>
+      </c>
+      <c r="AJ16" t="n">
         <v>0.9</v>
       </c>
-      <c r="AB16" t="n">
+      <c r="AK16" t="n">
         <v>0.5666666666666667</v>
       </c>
-      <c r="AC16" t="n">
+      <c r="AL16" t="n">
         <v>0.3</v>
       </c>
-      <c r="AD16" t="n">
+      <c r="AM16" t="n">
         <v>0.24</v>
       </c>
-      <c r="AE16" t="n">
+      <c r="AN16" t="n">
         <v>0.2333333333333333</v>
       </c>
-      <c r="AF16" t="n">
+      <c r="AO16" t="n">
         <v>0.2</v>
       </c>
-      <c r="AG16" t="n">
+      <c r="AP16" t="n">
         <v>0.1625</v>
       </c>
-      <c r="AH16" t="n">
+      <c r="AQ16" t="n">
         <v>0.1</v>
       </c>
-      <c r="AI16" t="n">
+      <c r="AR16" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AJ16" t="n">
+      <c r="AS16" t="n">
         <v>536.925</v>
       </c>
-      <c r="AK16" t="n">
+      <c r="AT16" t="n">
         <v>533.1333333333333</v>
       </c>
-      <c r="AL16" t="n">
+      <c r="AU16" t="n">
         <v>519.475</v>
       </c>
-      <c r="AM16" t="n">
+      <c r="AV16" t="n">
         <v>521</v>
       </c>
-      <c r="AN16" t="n">
+      <c r="AW16" t="n">
         <v>525.4083333333333</v>
       </c>
-      <c r="AO16" t="n">
+      <c r="AX16" t="n">
         <v>525.7071428571429</v>
       </c>
-      <c r="AP16" t="n">
+      <c r="AY16" t="n">
         <v>525.03125</v>
       </c>
-      <c r="AQ16" t="n">
+      <c r="AZ16" t="n">
         <v>520.6222222222223</v>
       </c>
-      <c r="AR16" t="n">
+      <c r="BA16" t="n">
         <v>518.29</v>
       </c>
-      <c r="AS16" t="n">
+      <c r="BB16" t="n">
         <v>25.599206530672</v>
       </c>
-      <c r="AT16" t="n">
+      <c r="BC16" t="n">
         <v>43.90917393387804</v>
       </c>
-      <c r="AU16" t="n">
+      <c r="BD16" t="n">
         <v>61.22192724016453</v>
       </c>
-      <c r="AV16" t="n">
+      <c r="BE16" t="n">
         <v>68.4697013283978</v>
       </c>
-      <c r="AW16" t="n">
+      <c r="BF16" t="n">
         <v>72.20716675341552</v>
       </c>
-      <c r="AX16" t="n">
+      <c r="BG16" t="n">
         <v>73.38844755609617</v>
       </c>
-      <c r="AY16" t="n">
+      <c r="BH16" t="n">
         <v>74.30010278214627</v>
       </c>
-      <c r="AZ16" t="n">
+      <c r="BI16" t="n">
         <v>77.32831560988335</v>
       </c>
-      <c r="BA16" t="n">
+      <c r="BJ16" t="n">
         <v>79.8353674758249</v>
       </c>
-      <c r="BB16" t="n">
+      <c r="BK16" t="n">
         <v>486</v>
       </c>
-      <c r="BC16" t="n">
+      <c r="BL16" t="n">
         <v>447</v>
       </c>
-      <c r="BD16" t="n">
+      <c r="BM16" t="n">
         <v>416</v>
       </c>
-      <c r="BE16" t="n">
+      <c r="BN16" t="n">
         <v>416</v>
       </c>
-      <c r="BF16" t="n">
+      <c r="BO16" t="n">
         <v>416</v>
       </c>
-      <c r="BG16" t="n">
+      <c r="BP16" t="n">
         <v>416</v>
       </c>
-      <c r="BH16" t="n">
+      <c r="BQ16" t="n">
         <v>416</v>
       </c>
-      <c r="BI16" t="n">
+      <c r="BR16" t="n">
         <v>402</v>
       </c>
-      <c r="BJ16" t="n">
+      <c r="BS16" t="n">
         <v>402</v>
       </c>
-      <c r="BK16" t="n">
+      <c r="BT16" t="n">
         <v>639</v>
       </c>
-      <c r="BL16" t="n">
+      <c r="BU16" t="n">
         <v>639</v>
       </c>
-      <c r="BM16" t="n">
+      <c r="BV16" t="n">
         <v>639</v>
       </c>
-      <c r="BN16" t="n">
+      <c r="BW16" t="n">
         <v>639</v>
       </c>
-      <c r="BO16" t="n">
+      <c r="BX16" t="n">
         <v>639</v>
       </c>
-      <c r="BP16" t="n">
+      <c r="BY16" t="n">
         <v>639</v>
       </c>
-      <c r="BQ16" t="n">
+      <c r="BZ16" t="n">
         <v>639</v>
       </c>
-      <c r="BR16" t="n">
+      <c r="CA16" t="n">
         <v>639</v>
       </c>
-      <c r="BS16" t="n">
+      <c r="CB16" t="n">
         <v>639</v>
       </c>
-      <c r="BT16" t="n">
+      <c r="CC16" t="n">
         <v>0.125</v>
       </c>
-      <c r="BU16" t="n">
+      <c r="CD16" t="n">
         <v>0.3636363636363636</v>
       </c>
-      <c r="BV16" t="n">
+      <c r="CE16" t="n">
         <v>0.7272727272727273</v>
       </c>
-      <c r="BW16" t="n">
+      <c r="CF16" t="n">
         <v>0.9166666666666666</v>
       </c>
-      <c r="BX16" t="n">
+      <c r="CG16" t="n">
         <v>0.875</v>
       </c>
-      <c r="BY16" t="n">
+      <c r="CH16" t="n">
         <v>0.7894736842105263</v>
       </c>
-      <c r="BZ16" t="n">
+      <c r="CI16" t="n">
         <v>0.9047619047619048</v>
       </c>
-      <c r="CA16" t="n">
+      <c r="CJ16" t="n">
         <v>0.96</v>
       </c>
-      <c r="CB16" t="n">
+      <c r="CK16" t="n">
         <v>1</v>
+      </c>
+      <c r="CL16" t="n">
+        <v>515.45</v>
+      </c>
+      <c r="CM16" t="n">
+        <v>86.2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S17_G6_501_62_ABS1</t>
+          <t>S16_G6_502_58_ABS1</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C17" t="n">
-        <v>62</v>
+        <v>85.9896219421794</v>
       </c>
       <c r="D17" t="n">
-        <v>91.91994069681246</v>
+        <v>58</v>
       </c>
       <c r="E17" t="n">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F17" t="n">
         <v>200</v>
       </c>
       <c r="G17" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="H17" t="inlineStr">
+        <v>77.5</v>
+      </c>
+      <c r="H17" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="I17" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="L17" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="M17" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="O17" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="P17" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="Q17" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I17" t="n">
-        <v>498.2166870914867</v>
-      </c>
-      <c r="J17" t="n">
-        <v>117.778792228543</v>
-      </c>
-      <c r="K17" t="n">
-        <v>498.4701457791709</v>
-      </c>
-      <c r="L17" t="n">
-        <v>80.35561107174948</v>
-      </c>
-      <c r="M17" t="n">
-        <v>494.4905407128017</v>
-      </c>
-      <c r="N17" t="n">
-        <v>73.19814968624733</v>
-      </c>
-      <c r="O17" t="n">
-        <v>494.2419883100156</v>
-      </c>
-      <c r="P17" t="n">
-        <v>71.492945783208</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>494.9956007769173</v>
-      </c>
       <c r="R17" t="n">
-        <v>71.05638720575693</v>
+        <v>472.72</v>
       </c>
       <c r="S17" t="n">
-        <v>491.3982048840783</v>
+        <v>332.87</v>
       </c>
       <c r="T17" t="n">
-        <v>75.51838982516814</v>
+        <v>506.56</v>
       </c>
       <c r="U17" t="n">
-        <v>486.1539330523862</v>
+        <v>117.51</v>
       </c>
       <c r="V17" t="n">
-        <v>70.17216175966749</v>
+        <v>503.01</v>
       </c>
       <c r="W17" t="n">
-        <v>483.5191452939308</v>
+        <v>98.27</v>
       </c>
       <c r="X17" t="n">
-        <v>77.03508906653407</v>
+        <v>488.22</v>
       </c>
       <c r="Y17" t="n">
-        <v>484.5637074864171</v>
+        <v>104.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>73.65470375205742</v>
+        <v>486.6</v>
       </c>
       <c r="AA17" t="n">
+        <v>91.34999999999999</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>493.65</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>85.63</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>495.43</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>86.20999999999999</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>489.36</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>82.38</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>490.16</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>79.2</v>
+      </c>
+      <c r="AJ17" t="n">
         <v>0</v>
       </c>
-      <c r="AB17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>-0.025</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>-0.01428571428571429</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>-0.02222222222222222</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>498.075</v>
-      </c>
       <c r="AK17" t="n">
-        <v>498.2666666666667</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="AL17" t="n">
-        <v>494.625</v>
+        <v>-0.075</v>
       </c>
       <c r="AM17" t="n">
-        <v>494.33</v>
+        <v>-0.14</v>
       </c>
       <c r="AN17" t="n">
-        <v>494.6916666666667</v>
+        <v>-0.1</v>
       </c>
       <c r="AO17" t="n">
-        <v>493.7928571428571</v>
+        <v>-0.07142857142857142</v>
       </c>
       <c r="AP17" t="n">
-        <v>493.925</v>
+        <v>-0.05</v>
       </c>
       <c r="AQ17" t="n">
-        <v>491.0777777777778</v>
+        <v>-0.04444444444444445</v>
       </c>
       <c r="AR17" t="n">
-        <v>491.085</v>
+        <v>-0.03</v>
       </c>
       <c r="AS17" t="n">
-        <v>68.28410777772527</v>
+        <v>523.025</v>
       </c>
       <c r="AT17" t="n">
-        <v>72.15166125753601</v>
+        <v>513.8666666666667</v>
       </c>
       <c r="AU17" t="n">
-        <v>74.93136442772146</v>
+        <v>508.0875</v>
       </c>
       <c r="AV17" t="n">
-        <v>74.41385018932966</v>
+        <v>496.98</v>
       </c>
       <c r="AW17" t="n">
-        <v>73.38151400197614</v>
+        <v>496.4083333333334</v>
       </c>
       <c r="AX17" t="n">
-        <v>73.40557554033728</v>
+        <v>496.3</v>
       </c>
       <c r="AY17" t="n">
-        <v>72.66202154495841</v>
+        <v>497.48125</v>
       </c>
       <c r="AZ17" t="n">
-        <v>72.39816261906985</v>
+        <v>497.2</v>
       </c>
       <c r="BA17" t="n">
-        <v>72.31084133793495</v>
+        <v>496.88</v>
       </c>
       <c r="BB17" t="n">
-        <v>355</v>
+        <v>59.92014999146781</v>
       </c>
       <c r="BC17" t="n">
-        <v>355</v>
+        <v>65.31856976048661</v>
       </c>
       <c r="BD17" t="n">
-        <v>355</v>
+        <v>74.59443574255388</v>
       </c>
       <c r="BE17" t="n">
-        <v>355</v>
+        <v>80.75666907444858</v>
       </c>
       <c r="BF17" t="n">
-        <v>355</v>
+        <v>83.39939006904601</v>
       </c>
       <c r="BG17" t="n">
-        <v>355</v>
+        <v>83.83569815844731</v>
       </c>
       <c r="BH17" t="n">
-        <v>355</v>
+        <v>83.51983086930613</v>
       </c>
       <c r="BI17" t="n">
-        <v>355</v>
+        <v>82.74810504711807</v>
       </c>
       <c r="BJ17" t="n">
-        <v>355</v>
+        <v>81.86101391993627</v>
       </c>
       <c r="BK17" t="n">
-        <v>653</v>
+        <v>446</v>
       </c>
       <c r="BL17" t="n">
-        <v>653</v>
+        <v>408</v>
       </c>
       <c r="BM17" t="n">
-        <v>653</v>
+        <v>394</v>
       </c>
       <c r="BN17" t="n">
-        <v>653</v>
+        <v>378</v>
       </c>
       <c r="BO17" t="n">
-        <v>653</v>
+        <v>375</v>
       </c>
       <c r="BP17" t="n">
-        <v>653</v>
+        <v>375</v>
       </c>
       <c r="BQ17" t="n">
-        <v>653</v>
+        <v>375</v>
       </c>
       <c r="BR17" t="n">
-        <v>653</v>
+        <v>375</v>
       </c>
       <c r="BS17" t="n">
-        <v>653</v>
+        <v>375</v>
       </c>
       <c r="BT17" t="n">
+        <v>627</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>627</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>627</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>627</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>627</v>
+      </c>
+      <c r="BY17" t="n">
+        <v>627</v>
+      </c>
+      <c r="BZ17" t="n">
+        <v>627</v>
+      </c>
+      <c r="CA17" t="n">
+        <v>627</v>
+      </c>
+      <c r="CB17" t="n">
+        <v>627</v>
+      </c>
+      <c r="CC17" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="BU17" t="n">
-        <v>0.8571428571428571</v>
-      </c>
-      <c r="BV17" t="n">
-        <v>1</v>
-      </c>
-      <c r="BW17" t="n">
-        <v>0.9565217391304348</v>
-      </c>
-      <c r="BX17" t="n">
-        <v>0.8888888888888888</v>
-      </c>
-      <c r="BY17" t="n">
+      <c r="CD17" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="CE17" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="CF17" t="n">
+        <v>0.7058823529411765</v>
+      </c>
+      <c r="CG17" t="n">
         <v>0.9411764705882353</v>
       </c>
-      <c r="BZ17" t="n">
-        <v>0.8974358974358975</v>
-      </c>
-      <c r="CA17" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="CB17" t="n">
-        <v>0.7916666666666666</v>
+      <c r="CH17" t="n">
+        <v>0.9047619047619048</v>
+      </c>
+      <c r="CI17" t="n">
+        <v>0.9545454545454546</v>
+      </c>
+      <c r="CJ17" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="CK17" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="CL17" t="n">
+        <v>490.16</v>
+      </c>
+      <c r="CM17" t="n">
+        <v>79.2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S18_G6_498_60_ABS1</t>
+          <t>S17_G6_501_62_ABS1</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="C18" t="n">
-        <v>60</v>
+        <v>91.91994069681246</v>
       </c>
       <c r="D18" t="n">
-        <v>88.95478131949592</v>
+        <v>62</v>
       </c>
       <c r="E18" t="n">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="F18" t="n">
         <v>200</v>
       </c>
       <c r="G18" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="H18" t="inlineStr">
+        <v>76.5</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="L18" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="M18" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="O18" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="Q18" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I18" t="n">
-        <v>491.1525548078471</v>
-      </c>
-      <c r="J18" t="n">
-        <v>41.32237942272068</v>
-      </c>
-      <c r="K18" t="n">
-        <v>505.8132504126233</v>
-      </c>
-      <c r="L18" t="n">
-        <v>57.78469835473354</v>
-      </c>
-      <c r="M18" t="n">
-        <v>517.8195855844236</v>
-      </c>
-      <c r="N18" t="n">
-        <v>70.19025379254856</v>
-      </c>
-      <c r="O18" t="n">
-        <v>514.478192918818</v>
-      </c>
-      <c r="P18" t="n">
-        <v>67.3995249749001</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>509.8443850273522</v>
-      </c>
       <c r="R18" t="n">
-        <v>65.77435318193238</v>
+        <v>498.22</v>
       </c>
       <c r="S18" t="n">
-        <v>509.303181192015</v>
+        <v>117.78</v>
       </c>
       <c r="T18" t="n">
-        <v>62.73038003817165</v>
+        <v>498.47</v>
       </c>
       <c r="U18" t="n">
-        <v>505.8833010120251</v>
+        <v>80.36</v>
       </c>
       <c r="V18" t="n">
-        <v>56.83519355344166</v>
+        <v>494.49</v>
       </c>
       <c r="W18" t="n">
-        <v>503.1297306293704</v>
+        <v>73.2</v>
       </c>
       <c r="X18" t="n">
-        <v>57.23025512066084</v>
+        <v>494.24</v>
       </c>
       <c r="Y18" t="n">
-        <v>506.0289273096678</v>
+        <v>71.48999999999999</v>
       </c>
       <c r="Z18" t="n">
-        <v>55.83663508562075</v>
+        <v>495</v>
       </c>
       <c r="AA18" t="n">
-        <v>-0.07692307692307693</v>
+        <v>71.06</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.05084745762711865</v>
+        <v>491.4</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.189873417721519</v>
+        <v>75.52</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.1515151515151515</v>
+        <v>486.15</v>
       </c>
       <c r="AE18" t="n">
-        <v>0.1092436974789916</v>
+        <v>70.17</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.09352517985611511</v>
+        <v>483.52</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.1069182389937107</v>
+        <v>77.04000000000001</v>
       </c>
       <c r="AH18" t="n">
-        <v>0.106145251396648</v>
+        <v>484.56</v>
       </c>
       <c r="AI18" t="n">
-        <v>0.09547738693467336</v>
+        <v>73.65000000000001</v>
       </c>
       <c r="AJ18" t="n">
-        <v>484</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>496.5666666666667</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>512.8</v>
+        <v>-0.025</v>
       </c>
       <c r="AM18" t="n">
-        <v>513.26</v>
+        <v>-0.02</v>
       </c>
       <c r="AN18" t="n">
-        <v>511.4916666666667</v>
+        <v>0</v>
       </c>
       <c r="AO18" t="n">
-        <v>510.6857142857143</v>
+        <v>-0.01428571428571429</v>
       </c>
       <c r="AP18" t="n">
-        <v>511.55</v>
+        <v>0</v>
       </c>
       <c r="AQ18" t="n">
-        <v>511.0277777777778</v>
+        <v>-0.02222222222222222</v>
       </c>
       <c r="AR18" t="n">
-        <v>510.4</v>
+        <v>-0.01</v>
       </c>
       <c r="AS18" t="n">
-        <v>52.05045629002689</v>
+        <v>498.075</v>
       </c>
       <c r="AT18" t="n">
-        <v>55.42994577743053</v>
+        <v>498.2666666666667</v>
       </c>
       <c r="AU18" t="n">
-        <v>64.75268334208243</v>
+        <v>494.625</v>
       </c>
       <c r="AV18" t="n">
-        <v>68.08680048291299</v>
+        <v>494.33</v>
       </c>
       <c r="AW18" t="n">
-        <v>68.03320216792844</v>
+        <v>494.6916666666667</v>
       </c>
       <c r="AX18" t="n">
-        <v>66.59280159664253</v>
+        <v>493.7928571428571</v>
       </c>
       <c r="AY18" t="n">
-        <v>65.09673570925044</v>
+        <v>493.925</v>
       </c>
       <c r="AZ18" t="n">
-        <v>63.27896179752667</v>
+        <v>491.0777777777778</v>
       </c>
       <c r="BA18" t="n">
-        <v>62.26250878337621</v>
+        <v>491.085</v>
       </c>
       <c r="BB18" t="n">
-        <v>354</v>
+        <v>68.28410777772527</v>
       </c>
       <c r="BC18" t="n">
-        <v>354</v>
+        <v>72.15166125753601</v>
       </c>
       <c r="BD18" t="n">
-        <v>354</v>
+        <v>74.93136442772146</v>
       </c>
       <c r="BE18" t="n">
-        <v>354</v>
+        <v>74.41385018932966</v>
       </c>
       <c r="BF18" t="n">
-        <v>354</v>
+        <v>73.38151400197614</v>
       </c>
       <c r="BG18" t="n">
-        <v>354</v>
+        <v>73.40557554033728</v>
       </c>
       <c r="BH18" t="n">
-        <v>354</v>
+        <v>72.66202154495841</v>
       </c>
       <c r="BI18" t="n">
-        <v>354</v>
+        <v>72.39816261906985</v>
       </c>
       <c r="BJ18" t="n">
-        <v>354</v>
+        <v>72.31084133793495</v>
       </c>
       <c r="BK18" t="n">
-        <v>568</v>
+        <v>355</v>
       </c>
       <c r="BL18" t="n">
-        <v>590</v>
+        <v>355</v>
       </c>
       <c r="BM18" t="n">
-        <v>617</v>
+        <v>355</v>
       </c>
       <c r="BN18" t="n">
-        <v>617</v>
+        <v>355</v>
       </c>
       <c r="BO18" t="n">
-        <v>617</v>
+        <v>355</v>
       </c>
       <c r="BP18" t="n">
-        <v>617</v>
+        <v>355</v>
       </c>
       <c r="BQ18" t="n">
-        <v>617</v>
+        <v>355</v>
       </c>
       <c r="BR18" t="n">
-        <v>617</v>
+        <v>355</v>
       </c>
       <c r="BS18" t="n">
-        <v>617</v>
+        <v>355</v>
       </c>
       <c r="BT18" t="n">
-        <v>0.6666666666666666</v>
+        <v>653</v>
       </c>
       <c r="BU18" t="n">
-        <v>0.7</v>
+        <v>653</v>
       </c>
       <c r="BV18" t="n">
+        <v>653</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>653</v>
+      </c>
+      <c r="BX18" t="n">
+        <v>653</v>
+      </c>
+      <c r="BY18" t="n">
+        <v>653</v>
+      </c>
+      <c r="BZ18" t="n">
+        <v>653</v>
+      </c>
+      <c r="CA18" t="n">
+        <v>653</v>
+      </c>
+      <c r="CB18" t="n">
+        <v>653</v>
+      </c>
+      <c r="CC18" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="CD18" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="CE18" t="n">
         <v>1</v>
       </c>
-      <c r="BW18" t="n">
-        <v>0.7333333333333333</v>
-      </c>
-      <c r="BX18" t="n">
-        <v>0.7142857142857143</v>
-      </c>
-      <c r="BY18" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="BZ18" t="n">
-        <v>0.6923076923076923</v>
-      </c>
-      <c r="CA18" t="n">
-        <v>0.8214285714285714</v>
-      </c>
-      <c r="CB18" t="n">
-        <v>0.9375</v>
+      <c r="CF18" t="n">
+        <v>0.9565217391304348</v>
+      </c>
+      <c r="CG18" t="n">
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="CH18" t="n">
+        <v>0.9411764705882353</v>
+      </c>
+      <c r="CI18" t="n">
+        <v>0.8974358974358975</v>
+      </c>
+      <c r="CJ18" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="CK18" t="n">
+        <v>0.7916666666666666</v>
+      </c>
+      <c r="CL18" t="n">
+        <v>484.56</v>
+      </c>
+      <c r="CM18" t="n">
+        <v>73.65000000000001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S16_G6_502_58_ABS1</t>
+          <t>S18_G6_498_60_ABS1</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="C19" t="n">
-        <v>58</v>
+        <v>88.95478131949592</v>
       </c>
       <c r="D19" t="n">
-        <v>85.9896219421794</v>
+        <v>60</v>
       </c>
       <c r="E19" t="n">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="F19" t="n">
         <v>200</v>
       </c>
       <c r="G19" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="H19" t="inlineStr">
+        <v>78.5</v>
+      </c>
+      <c r="H19" t="n">
+        <v>3</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="L19" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="M19" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="N19" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="O19" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="P19" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="Q19" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I19" t="n">
-        <v>472.7172351976528</v>
-      </c>
-      <c r="J19" t="n">
-        <v>332.8722188228058</v>
-      </c>
-      <c r="K19" t="n">
-        <v>506.556852893842</v>
-      </c>
-      <c r="L19" t="n">
-        <v>117.5095672223694</v>
-      </c>
-      <c r="M19" t="n">
-        <v>503.0147422180816</v>
-      </c>
-      <c r="N19" t="n">
-        <v>98.26685898748981</v>
-      </c>
-      <c r="O19" t="n">
-        <v>488.2184375005154</v>
-      </c>
-      <c r="P19" t="n">
-        <v>104.4981469169218</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>486.60346075356</v>
-      </c>
       <c r="R19" t="n">
-        <v>91.35423448328943</v>
+        <v>491.15</v>
       </c>
       <c r="S19" t="n">
-        <v>493.6469047263359</v>
+        <v>41.32</v>
       </c>
       <c r="T19" t="n">
-        <v>85.62709184680725</v>
+        <v>505.81</v>
       </c>
       <c r="U19" t="n">
-        <v>495.4280717394413</v>
+        <v>57.78</v>
       </c>
       <c r="V19" t="n">
-        <v>86.20860046197494</v>
+        <v>517.8200000000001</v>
       </c>
       <c r="W19" t="n">
-        <v>489.360034442363</v>
+        <v>70.19</v>
       </c>
       <c r="X19" t="n">
-        <v>82.37655531668399</v>
+        <v>514.48</v>
       </c>
       <c r="Y19" t="n">
-        <v>490.1587853836763</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="Z19" t="n">
-        <v>79.20119473901876</v>
+        <v>509.84</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>65.77</v>
       </c>
       <c r="AB19" t="n">
-        <v>-0.06666666666666667</v>
+        <v>509.3</v>
       </c>
       <c r="AC19" t="n">
-        <v>-0.075</v>
+        <v>62.73</v>
       </c>
       <c r="AD19" t="n">
-        <v>-0.14</v>
+        <v>505.88</v>
       </c>
       <c r="AE19" t="n">
-        <v>-0.1</v>
+        <v>56.84</v>
       </c>
       <c r="AF19" t="n">
-        <v>-0.07142857142857142</v>
+        <v>503.13</v>
       </c>
       <c r="AG19" t="n">
-        <v>-0.05</v>
+        <v>57.23</v>
       </c>
       <c r="AH19" t="n">
-        <v>-0.04444444444444445</v>
+        <v>506.03</v>
       </c>
       <c r="AI19" t="n">
-        <v>-0.03</v>
+        <v>55.84</v>
       </c>
       <c r="AJ19" t="n">
-        <v>523.025</v>
+        <v>-0.07692307692307693</v>
       </c>
       <c r="AK19" t="n">
-        <v>513.8666666666667</v>
+        <v>0.05084745762711865</v>
       </c>
       <c r="AL19" t="n">
-        <v>508.0875</v>
+        <v>0.189873417721519</v>
       </c>
       <c r="AM19" t="n">
-        <v>496.98</v>
+        <v>0.1515151515151515</v>
       </c>
       <c r="AN19" t="n">
-        <v>496.4083333333334</v>
+        <v>0.1092436974789916</v>
       </c>
       <c r="AO19" t="n">
-        <v>496.3</v>
+        <v>0.09352517985611511</v>
       </c>
       <c r="AP19" t="n">
-        <v>497.48125</v>
+        <v>0.1069182389937107</v>
       </c>
       <c r="AQ19" t="n">
-        <v>497.2</v>
+        <v>0.106145251396648</v>
       </c>
       <c r="AR19" t="n">
-        <v>496.88</v>
+        <v>0.09547738693467336</v>
       </c>
       <c r="AS19" t="n">
-        <v>59.92014999146781</v>
+        <v>484</v>
       </c>
       <c r="AT19" t="n">
-        <v>65.31856976048661</v>
+        <v>496.5666666666667</v>
       </c>
       <c r="AU19" t="n">
-        <v>74.59443574255388</v>
+        <v>512.8</v>
       </c>
       <c r="AV19" t="n">
-        <v>80.75666907444858</v>
+        <v>513.26</v>
       </c>
       <c r="AW19" t="n">
-        <v>83.39939006904601</v>
+        <v>511.4916666666667</v>
       </c>
       <c r="AX19" t="n">
-        <v>83.83569815844731</v>
+        <v>510.6857142857143</v>
       </c>
       <c r="AY19" t="n">
-        <v>83.51983086930613</v>
+        <v>511.55</v>
       </c>
       <c r="AZ19" t="n">
-        <v>82.74810504711807</v>
+        <v>511.0277777777778</v>
       </c>
       <c r="BA19" t="n">
-        <v>81.86101391993627</v>
+        <v>510.4</v>
       </c>
       <c r="BB19" t="n">
-        <v>446</v>
+        <v>52.05045629002689</v>
       </c>
       <c r="BC19" t="n">
-        <v>408</v>
+        <v>55.42994577743053</v>
       </c>
       <c r="BD19" t="n">
-        <v>394</v>
+        <v>64.75268334208243</v>
       </c>
       <c r="BE19" t="n">
-        <v>378</v>
+        <v>68.08680048291299</v>
       </c>
       <c r="BF19" t="n">
-        <v>375</v>
+        <v>68.03320216792844</v>
       </c>
       <c r="BG19" t="n">
-        <v>375</v>
+        <v>66.59280159664253</v>
       </c>
       <c r="BH19" t="n">
-        <v>375</v>
+        <v>65.09673570925044</v>
       </c>
       <c r="BI19" t="n">
-        <v>375</v>
+        <v>63.27896179752667</v>
       </c>
       <c r="BJ19" t="n">
-        <v>375</v>
+        <v>62.26250878337621</v>
       </c>
       <c r="BK19" t="n">
-        <v>627</v>
+        <v>354</v>
       </c>
       <c r="BL19" t="n">
-        <v>627</v>
+        <v>354</v>
       </c>
       <c r="BM19" t="n">
-        <v>627</v>
+        <v>354</v>
       </c>
       <c r="BN19" t="n">
-        <v>627</v>
+        <v>354</v>
       </c>
       <c r="BO19" t="n">
-        <v>627</v>
+        <v>354</v>
       </c>
       <c r="BP19" t="n">
-        <v>627</v>
+        <v>354</v>
       </c>
       <c r="BQ19" t="n">
-        <v>627</v>
+        <v>354</v>
       </c>
       <c r="BR19" t="n">
-        <v>627</v>
+        <v>354</v>
       </c>
       <c r="BS19" t="n">
-        <v>627</v>
+        <v>354</v>
       </c>
       <c r="BT19" t="n">
-        <v>0.5714285714285714</v>
+        <v>568</v>
       </c>
       <c r="BU19" t="n">
-        <v>0.875</v>
+        <v>590</v>
       </c>
       <c r="BV19" t="n">
-        <v>0.8</v>
+        <v>617</v>
       </c>
       <c r="BW19" t="n">
-        <v>0.7058823529411765</v>
+        <v>617</v>
       </c>
       <c r="BX19" t="n">
-        <v>0.9411764705882353</v>
+        <v>617</v>
       </c>
       <c r="BY19" t="n">
-        <v>0.9047619047619048</v>
+        <v>617</v>
       </c>
       <c r="BZ19" t="n">
-        <v>0.9545454545454546</v>
+        <v>617</v>
       </c>
       <c r="CA19" t="n">
-        <v>0.75</v>
+        <v>617</v>
       </c>
       <c r="CB19" t="n">
+        <v>617</v>
+      </c>
+      <c r="CC19" t="n">
         <v>0.6666666666666666</v>
+      </c>
+      <c r="CD19" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="CE19" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF19" t="n">
+        <v>0.7333333333333333</v>
+      </c>
+      <c r="CG19" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="CH19" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="CI19" t="n">
+        <v>0.6923076923076923</v>
+      </c>
+      <c r="CJ19" t="n">
+        <v>0.8214285714285714</v>
+      </c>
+      <c r="CK19" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="CL19" t="n">
+        <v>506.03</v>
+      </c>
+      <c r="CM19" t="n">
+        <v>55.84</v>
       </c>
     </row>
     <row r="20">
@@ -5268,10 +5917,10 @@
         <v>499</v>
       </c>
       <c r="C20" t="n">
+        <v>88.95478131949592</v>
+      </c>
+      <c r="D20" t="n">
         <v>60</v>
-      </c>
-      <c r="D20" t="n">
-        <v>88.95478131949592</v>
       </c>
       <c r="E20" t="n">
         <v>499</v>
@@ -5280,228 +5929,261 @@
         <v>200</v>
       </c>
       <c r="G20" t="n">
-        <v>0.495</v>
-      </c>
-      <c r="H20" t="inlineStr">
+        <v>72</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="L20" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="M20" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="O20" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Q20" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I20" t="n">
-        <v>510.6908268151361</v>
-      </c>
-      <c r="J20" t="n">
-        <v>22.77070054636285</v>
-      </c>
-      <c r="K20" t="n">
-        <v>498.3638213665711</v>
-      </c>
-      <c r="L20" t="n">
-        <v>52.72543248532767</v>
-      </c>
-      <c r="M20" t="n">
-        <v>491.9299891638066</v>
-      </c>
-      <c r="N20" t="n">
-        <v>52.2685041221871</v>
-      </c>
-      <c r="O20" t="n">
-        <v>494.2559905862718</v>
-      </c>
-      <c r="P20" t="n">
-        <v>48.42111132377978</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>493.9262805864044</v>
-      </c>
       <c r="R20" t="n">
-        <v>44.66085116597171</v>
+        <v>510.69</v>
       </c>
       <c r="S20" t="n">
-        <v>495.0196808430403</v>
+        <v>22.77</v>
       </c>
       <c r="T20" t="n">
-        <v>43.15972164174627</v>
+        <v>498.36</v>
       </c>
       <c r="U20" t="n">
-        <v>503.6099094881426</v>
+        <v>52.73</v>
       </c>
       <c r="V20" t="n">
-        <v>52.91532795844553</v>
+        <v>491.93</v>
       </c>
       <c r="W20" t="n">
-        <v>503.8054242272316</v>
+        <v>52.27</v>
       </c>
       <c r="X20" t="n">
-        <v>56.5487071485441</v>
+        <v>494.26</v>
       </c>
       <c r="Y20" t="n">
-        <v>500.877015200147</v>
+        <v>48.42</v>
       </c>
       <c r="Z20" t="n">
-        <v>57.98526746577163</v>
+        <v>493.93</v>
       </c>
       <c r="AA20" t="n">
+        <v>44.66</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>495.02</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>43.16</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>503.61</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>52.92</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>503.81</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>56.55</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>500.88</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>57.99</v>
+      </c>
+      <c r="AJ20" t="n">
         <v>0.5</v>
       </c>
-      <c r="AB20" t="n">
+      <c r="AK20" t="n">
         <v>0.06666666666666667</v>
       </c>
-      <c r="AC20" t="n">
+      <c r="AL20" t="n">
         <v>-0.075</v>
       </c>
-      <c r="AD20" t="n">
+      <c r="AM20" t="n">
         <v>-0.06</v>
       </c>
-      <c r="AE20" t="n">
+      <c r="AN20" t="n">
         <v>-0.06666666666666667</v>
       </c>
-      <c r="AF20" t="n">
+      <c r="AO20" t="n">
         <v>-0.07142857142857142</v>
       </c>
-      <c r="AG20" t="n">
+      <c r="AP20" t="n">
         <v>0.05</v>
       </c>
-      <c r="AH20" t="n">
+      <c r="AQ20" t="n">
         <v>0.04444444444444445</v>
       </c>
-      <c r="AI20" t="n">
+      <c r="AR20" t="n">
         <v>0.03</v>
       </c>
-      <c r="AJ20" t="n">
+      <c r="AS20" t="n">
         <v>518.25</v>
       </c>
-      <c r="AK20" t="n">
+      <c r="AT20" t="n">
         <v>498.6833333333333</v>
       </c>
-      <c r="AL20" t="n">
+      <c r="AU20" t="n">
         <v>490.175</v>
       </c>
-      <c r="AM20" t="n">
+      <c r="AV20" t="n">
         <v>490.93</v>
       </c>
-      <c r="AN20" t="n">
+      <c r="AW20" t="n">
         <v>491.5083333333333</v>
       </c>
-      <c r="AO20" t="n">
+      <c r="AX20" t="n">
         <v>491.7785714285714</v>
       </c>
-      <c r="AP20" t="n">
+      <c r="AY20" t="n">
         <v>499.20625</v>
       </c>
-      <c r="AQ20" t="n">
+      <c r="AZ20" t="n">
         <v>499.8555555555556</v>
       </c>
-      <c r="AR20" t="n">
+      <c r="BA20" t="n">
         <v>499.82</v>
       </c>
-      <c r="AS20" t="n">
+      <c r="BB20" t="n">
         <v>29.51842644857615</v>
       </c>
-      <c r="AT20" t="n">
+      <c r="BC20" t="n">
         <v>43.37875504079029</v>
       </c>
-      <c r="AU20" t="n">
+      <c r="BD20" t="n">
         <v>48.974425724045</v>
       </c>
-      <c r="AV20" t="n">
+      <c r="BE20" t="n">
         <v>50.92450392492793</v>
       </c>
-      <c r="AW20" t="n">
+      <c r="BF20" t="n">
         <v>50.25866357046205</v>
       </c>
-      <c r="AX20" t="n">
+      <c r="BG20" t="n">
         <v>49.42094233031505</v>
       </c>
-      <c r="AY20" t="n">
+      <c r="BH20" t="n">
         <v>51.22671384090043</v>
       </c>
-      <c r="AZ20" t="n">
+      <c r="BI20" t="n">
         <v>51.93426638252781</v>
       </c>
-      <c r="BA20" t="n">
+      <c r="BJ20" t="n">
         <v>53.4670702395409</v>
       </c>
-      <c r="BB20" t="n">
+      <c r="BK20" t="n">
         <v>484</v>
       </c>
-      <c r="BC20" t="n">
+      <c r="BL20" t="n">
         <v>416</v>
       </c>
-      <c r="BD20" t="n">
+      <c r="BM20" t="n">
         <v>416</v>
       </c>
-      <c r="BE20" t="n">
+      <c r="BN20" t="n">
         <v>416</v>
       </c>
-      <c r="BF20" t="n">
+      <c r="BO20" t="n">
         <v>416</v>
       </c>
-      <c r="BG20" t="n">
+      <c r="BP20" t="n">
         <v>416</v>
       </c>
-      <c r="BH20" t="n">
+      <c r="BQ20" t="n">
         <v>416</v>
       </c>
-      <c r="BI20" t="n">
+      <c r="BR20" t="n">
         <v>416</v>
       </c>
-      <c r="BJ20" t="n">
+      <c r="BS20" t="n">
         <v>416</v>
       </c>
-      <c r="BK20" t="n">
+      <c r="BT20" t="n">
         <v>651</v>
       </c>
-      <c r="BL20" t="n">
+      <c r="BU20" t="n">
         <v>651</v>
       </c>
-      <c r="BM20" t="n">
+      <c r="BV20" t="n">
         <v>651</v>
       </c>
-      <c r="BN20" t="n">
+      <c r="BW20" t="n">
         <v>651</v>
       </c>
-      <c r="BO20" t="n">
+      <c r="BX20" t="n">
         <v>651</v>
       </c>
-      <c r="BP20" t="n">
+      <c r="BY20" t="n">
         <v>651</v>
       </c>
-      <c r="BQ20" t="n">
+      <c r="BZ20" t="n">
         <v>651</v>
       </c>
-      <c r="BR20" t="n">
+      <c r="CA20" t="n">
         <v>651</v>
       </c>
-      <c r="BS20" t="n">
+      <c r="CB20" t="n">
         <v>651</v>
       </c>
-      <c r="BT20" t="n">
+      <c r="CC20" t="n">
         <v>1</v>
       </c>
-      <c r="BU20" t="n">
+      <c r="CD20" t="n">
         <v>0.8181818181818182</v>
       </c>
-      <c r="BV20" t="n">
+      <c r="CE20" t="n">
         <v>0.8181818181818182</v>
       </c>
-      <c r="BW20" t="n">
+      <c r="CF20" t="n">
         <v>0.9166666666666666</v>
       </c>
-      <c r="BX20" t="n">
+      <c r="CG20" t="n">
         <v>0.7857142857142857</v>
       </c>
-      <c r="BY20" t="n">
+      <c r="CH20" t="n">
         <v>0.7222222222222222</v>
       </c>
-      <c r="BZ20" t="n">
+      <c r="CI20" t="n">
         <v>0.95</v>
       </c>
-      <c r="CA20" t="n">
+      <c r="CJ20" t="n">
         <v>0.8148148148148148</v>
       </c>
-      <c r="CB20" t="n">
+      <c r="CK20" t="n">
         <v>0.8275862068965517</v>
+      </c>
+      <c r="CL20" t="n">
+        <v>500.88</v>
+      </c>
+      <c r="CM20" t="n">
+        <v>57.99</v>
       </c>
     </row>
     <row r="21">
@@ -5514,10 +6196,10 @@
         <v>502</v>
       </c>
       <c r="C21" t="n">
+        <v>88.95478131949592</v>
+      </c>
+      <c r="D21" t="n">
         <v>60</v>
-      </c>
-      <c r="D21" t="n">
-        <v>88.95478131949592</v>
       </c>
       <c r="E21" t="n">
         <v>502</v>
@@ -5526,228 +6208,261 @@
         <v>200</v>
       </c>
       <c r="G21" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="H21" t="inlineStr">
+        <v>78</v>
+      </c>
+      <c r="H21" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="L21" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="M21" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="O21" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="P21" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q21" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I21" t="n">
-        <v>518.8565414254718</v>
-      </c>
-      <c r="J21" t="n">
-        <v>48.82886968619341</v>
-      </c>
-      <c r="K21" t="n">
-        <v>525.1488614468673</v>
-      </c>
-      <c r="L21" t="n">
-        <v>51.62588393540982</v>
-      </c>
-      <c r="M21" t="n">
-        <v>513.0309943077026</v>
-      </c>
-      <c r="N21" t="n">
-        <v>66.47179559131388</v>
-      </c>
-      <c r="O21" t="n">
-        <v>499.9360363010106</v>
-      </c>
-      <c r="P21" t="n">
-        <v>81.24156775534482</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>499.8156403188581</v>
-      </c>
       <c r="R21" t="n">
-        <v>65.25311870194992</v>
+        <v>518.86</v>
       </c>
       <c r="S21" t="n">
-        <v>497.1886553287577</v>
+        <v>48.83</v>
       </c>
       <c r="T21" t="n">
-        <v>77.85079498637695</v>
+        <v>525.15</v>
       </c>
       <c r="U21" t="n">
-        <v>493.3742698008689</v>
+        <v>51.63</v>
       </c>
       <c r="V21" t="n">
-        <v>71.46413135219275</v>
+        <v>513.03</v>
       </c>
       <c r="W21" t="n">
-        <v>493.0620779668541</v>
+        <v>66.47</v>
       </c>
       <c r="X21" t="n">
-        <v>67.11411210809075</v>
+        <v>499.94</v>
       </c>
       <c r="Y21" t="n">
-        <v>492.3874140835052</v>
+        <v>81.23999999999999</v>
       </c>
       <c r="Z21" t="n">
-        <v>65.31128807739169</v>
+        <v>499.82</v>
       </c>
       <c r="AA21" t="n">
+        <v>65.25</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>497.19</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>77.84999999999999</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>493.37</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>71.45999999999999</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>493.06</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>67.11</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>492.39</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>65.31</v>
+      </c>
+      <c r="AJ21" t="n">
         <v>0.15</v>
       </c>
-      <c r="AB21" t="n">
+      <c r="AK21" t="n">
         <v>0.1</v>
       </c>
-      <c r="AC21" t="n">
+      <c r="AL21" t="n">
         <v>0</v>
       </c>
-      <c r="AD21" t="n">
+      <c r="AM21" t="n">
         <v>-0.1</v>
       </c>
-      <c r="AE21" t="n">
+      <c r="AN21" t="n">
         <v>-0.08333333333333333</v>
       </c>
-      <c r="AF21" t="n">
+      <c r="AO21" t="n">
         <v>-0.1</v>
       </c>
-      <c r="AG21" t="n">
+      <c r="AP21" t="n">
         <v>-0.08749999999999999</v>
       </c>
-      <c r="AH21" t="n">
+      <c r="AQ21" t="n">
         <v>-0.07777777777777778</v>
       </c>
-      <c r="AI21" t="n">
+      <c r="AR21" t="n">
         <v>-0.06</v>
       </c>
-      <c r="AJ21" t="n">
+      <c r="AS21" t="n">
         <v>514.3</v>
       </c>
-      <c r="AK21" t="n">
+      <c r="AT21" t="n">
         <v>518.2666666666667</v>
       </c>
-      <c r="AL21" t="n">
+      <c r="AU21" t="n">
         <v>514</v>
       </c>
-      <c r="AM21" t="n">
+      <c r="AV21" t="n">
         <v>504.19</v>
       </c>
-      <c r="AN21" t="n">
+      <c r="AW21" t="n">
         <v>503.6</v>
       </c>
-      <c r="AO21" t="n">
+      <c r="AX21" t="n">
         <v>500.5857142857143</v>
       </c>
-      <c r="AP21" t="n">
+      <c r="AY21" t="n">
         <v>500.34375</v>
       </c>
-      <c r="AQ21" t="n">
+      <c r="AZ21" t="n">
         <v>499.2888888888889</v>
       </c>
-      <c r="AR21" t="n">
+      <c r="BA21" t="n">
         <v>499.265</v>
       </c>
-      <c r="AS21" t="n">
+      <c r="BB21" t="n">
         <v>56.82965775015718</v>
       </c>
-      <c r="AT21" t="n">
+      <c r="BC21" t="n">
         <v>54.95691241529333</v>
       </c>
-      <c r="AU21" t="n">
+      <c r="BD21" t="n">
         <v>57.86816914332093</v>
       </c>
-      <c r="AV21" t="n">
+      <c r="BE21" t="n">
         <v>65.14133787388774</v>
       </c>
-      <c r="AW21" t="n">
+      <c r="BF21" t="n">
         <v>67.6865816342747</v>
       </c>
-      <c r="AX21" t="n">
+      <c r="BG21" t="n">
         <v>69.85372325840065</v>
       </c>
-      <c r="AY21" t="n">
+      <c r="BH21" t="n">
         <v>70.8561083177555</v>
       </c>
-      <c r="AZ21" t="n">
+      <c r="BI21" t="n">
         <v>71.06276481540721</v>
       </c>
-      <c r="BA21" t="n">
+      <c r="BJ21" t="n">
         <v>69.78821372552818</v>
       </c>
-      <c r="BB21" t="n">
+      <c r="BK21" t="n">
         <v>424</v>
       </c>
-      <c r="BC21" t="n">
+      <c r="BL21" t="n">
         <v>424</v>
       </c>
-      <c r="BD21" t="n">
+      <c r="BM21" t="n">
         <v>421</v>
       </c>
-      <c r="BE21" t="n">
+      <c r="BN21" t="n">
         <v>394</v>
       </c>
-      <c r="BF21" t="n">
+      <c r="BO21" t="n">
         <v>394</v>
       </c>
-      <c r="BG21" t="n">
+      <c r="BP21" t="n">
         <v>392</v>
       </c>
-      <c r="BH21" t="n">
+      <c r="BQ21" t="n">
         <v>392</v>
       </c>
-      <c r="BI21" t="n">
+      <c r="BR21" t="n">
         <v>392</v>
       </c>
-      <c r="BJ21" t="n">
+      <c r="BS21" t="n">
         <v>392</v>
       </c>
-      <c r="BK21" t="n">
+      <c r="BT21" t="n">
         <v>653</v>
       </c>
-      <c r="BL21" t="n">
+      <c r="BU21" t="n">
         <v>653</v>
       </c>
-      <c r="BM21" t="n">
+      <c r="BV21" t="n">
         <v>653</v>
       </c>
-      <c r="BN21" t="n">
+      <c r="BW21" t="n">
         <v>653</v>
       </c>
-      <c r="BO21" t="n">
+      <c r="BX21" t="n">
         <v>653</v>
       </c>
-      <c r="BP21" t="n">
+      <c r="BY21" t="n">
         <v>653</v>
       </c>
-      <c r="BQ21" t="n">
+      <c r="BZ21" t="n">
         <v>653</v>
       </c>
-      <c r="BR21" t="n">
+      <c r="CA21" t="n">
         <v>653</v>
       </c>
-      <c r="BS21" t="n">
+      <c r="CB21" t="n">
         <v>653</v>
       </c>
-      <c r="BT21" t="n">
+      <c r="CC21" t="n">
         <v>0.5</v>
       </c>
-      <c r="BU21" t="n">
+      <c r="CD21" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="BV21" t="n">
+      <c r="CE21" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="BW21" t="n">
+      <c r="CF21" t="n">
         <v>1</v>
       </c>
-      <c r="BX21" t="n">
+      <c r="CG21" t="n">
         <v>0.9333333333333333</v>
       </c>
-      <c r="BY21" t="n">
+      <c r="CH21" t="n">
         <v>0.8947368421052632</v>
       </c>
-      <c r="BZ21" t="n">
+      <c r="CI21" t="n">
         <v>1</v>
       </c>
-      <c r="CA21" t="n">
+      <c r="CJ21" t="n">
         <v>0.8888888888888888</v>
       </c>
-      <c r="CB21" t="n">
+      <c r="CK21" t="n">
         <v>0.8275862068965517</v>
+      </c>
+      <c r="CL21" t="n">
+        <v>492.39</v>
+      </c>
+      <c r="CM21" t="n">
+        <v>65.31</v>
       </c>
     </row>
     <row r="22">
@@ -5760,10 +6475,10 @@
         <v>499.85</v>
       </c>
       <c r="C22" t="n">
+        <v>88.95478131949592</v>
+      </c>
+      <c r="D22" t="n">
         <v>60</v>
-      </c>
-      <c r="D22" t="n">
-        <v>88.95478131949592</v>
       </c>
       <c r="E22" t="n">
         <v>499.85</v>
@@ -5772,224 +6487,239 @@
         <v>200</v>
       </c>
       <c r="G22" t="n">
-        <v>0.5039999999999999</v>
-      </c>
-      <c r="H22" t="inlineStr"/>
+        <v>76.02500000000001</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.879</v>
+      </c>
       <c r="I22" t="n">
-        <v>507.2678643983879</v>
+        <v>2.835</v>
       </c>
       <c r="J22" t="n">
-        <v>72.26844620809199</v>
+        <v>2.793</v>
       </c>
       <c r="K22" t="n">
-        <v>505.137876266958</v>
+        <v>2.758</v>
       </c>
       <c r="L22" t="n">
-        <v>67.81207935368987</v>
+        <v>2.7185</v>
       </c>
       <c r="M22" t="n">
-        <v>504.0193236436178</v>
+        <v>2.684</v>
       </c>
       <c r="N22" t="n">
-        <v>69.72748756165151</v>
+        <v>2.801</v>
       </c>
       <c r="O22" t="n">
-        <v>502.376845343619</v>
+        <v>2.896</v>
       </c>
       <c r="P22" t="n">
-        <v>70.07614859780874</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>503.4703437544459</v>
-      </c>
+        <v>2.907</v>
+      </c>
+      <c r="Q22" t="inlineStr"/>
       <c r="R22" t="n">
-        <v>69.32437861020163</v>
+        <v>507.268</v>
       </c>
       <c r="S22" t="n">
-        <v>503.2912655453314</v>
+        <v>72.26849999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>69.095074630456</v>
+        <v>505.1375</v>
       </c>
       <c r="U22" t="n">
-        <v>502.3576287189086</v>
+        <v>67.8125</v>
       </c>
       <c r="V22" t="n">
-        <v>69.18907776576579</v>
+        <v>504.0185</v>
       </c>
       <c r="W22" t="n">
-        <v>501.4193754736888</v>
+        <v>69.72800000000001</v>
       </c>
       <c r="X22" t="n">
-        <v>70.61754018020707</v>
+        <v>502.3775000000001</v>
       </c>
       <c r="Y22" t="n">
-        <v>501.6046398136129</v>
+        <v>70.07599999999999</v>
       </c>
       <c r="Z22" t="n">
-        <v>69.5376391892526</v>
+        <v>503.47</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.1068218623481781</v>
+        <v>69.324</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.03609779855834794</v>
+        <v>503.292</v>
       </c>
       <c r="AC22" t="n">
-        <v>0.001863031483284644</v>
+        <v>69.0955</v>
       </c>
       <c r="AD22" t="n">
-        <v>-0.005507318078746652</v>
+        <v>502.3570000000001</v>
       </c>
       <c r="AE22" t="n">
-        <v>0.007162916013863171</v>
+        <v>69.1885</v>
       </c>
       <c r="AF22" t="n">
-        <v>0.001109373370868523</v>
+        <v>501.419</v>
       </c>
       <c r="AG22" t="n">
-        <v>0.005337751771355785</v>
+        <v>70.61699999999999</v>
       </c>
       <c r="AH22" t="n">
-        <v>-0.001933790861981185</v>
+        <v>501.6054999999999</v>
       </c>
       <c r="AI22" t="n">
-        <v>0.001786381401959291</v>
+        <v>69.53700000000001</v>
       </c>
       <c r="AJ22" t="n">
+        <v>0.107</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>0.03549999999999999</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>0.001000000000000002</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>-0.005500000000000001</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0.0009999999999999996</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>-0.0004999999999999998</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>0.002500000000000001</v>
+      </c>
+      <c r="AS22" t="n">
         <v>507.735</v>
       </c>
-      <c r="AK22" t="n">
+      <c r="AT22" t="n">
         <v>505.6125</v>
       </c>
-      <c r="AL22" t="n">
-        <v>503.4774999999998</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>502.6175</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>503.4191666666667</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>503.1421428571429</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>503.3684375</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>502.695</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>502.80875</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>53.49120887841683</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>59.04193091573641</v>
-      </c>
       <c r="AU22" t="n">
-        <v>63.76058635096647</v>
+        <v>503.477</v>
       </c>
       <c r="AV22" t="n">
-        <v>66.49378603668825</v>
+        <v>502.6175000000001</v>
       </c>
       <c r="AW22" t="n">
-        <v>67.60327341315019</v>
+        <v>503.4195000000001</v>
       </c>
       <c r="AX22" t="n">
-        <v>68.0461311998219</v>
+        <v>503.1420000000001</v>
       </c>
       <c r="AY22" t="n">
-        <v>68.50618185555058</v>
+        <v>503.3684999999999</v>
       </c>
       <c r="AZ22" t="n">
-        <v>68.78906921004405</v>
+        <v>502.6960000000001</v>
       </c>
       <c r="BA22" t="n">
-        <v>68.87993928192739</v>
+        <v>502.807</v>
       </c>
       <c r="BB22" t="n">
+        <v>53.491</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>59.04150000000001</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>63.76000000000001</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>66.49350000000001</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>67.60299999999999</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>68.04600000000001</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>68.50749999999999</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>68.7895</v>
+      </c>
+      <c r="BJ22" t="n">
+        <v>68.881</v>
+      </c>
+      <c r="BK22" t="n">
         <v>389.05</v>
       </c>
-      <c r="BC22" t="n">
+      <c r="BL22" t="n">
         <v>379.2</v>
       </c>
-      <c r="BD22" t="n">
+      <c r="BM22" t="n">
         <v>375.9</v>
       </c>
-      <c r="BE22" t="n">
+      <c r="BN22" t="n">
         <v>373</v>
       </c>
-      <c r="BF22" t="n">
+      <c r="BO22" t="n">
         <v>372.15</v>
       </c>
-      <c r="BG22" t="n">
+      <c r="BP22" t="n">
         <v>372.05</v>
       </c>
-      <c r="BH22" t="n">
+      <c r="BQ22" t="n">
         <v>371.8</v>
       </c>
-      <c r="BI22" t="n">
+      <c r="BR22" t="n">
         <v>370.85</v>
       </c>
-      <c r="BJ22" t="n">
+      <c r="BS22" t="n">
         <v>370.85</v>
       </c>
-      <c r="BK22" t="n">
+      <c r="BT22" t="n">
         <v>618.85</v>
       </c>
-      <c r="BL22" t="n">
+      <c r="BU22" t="n">
         <v>622.05</v>
       </c>
-      <c r="BM22" t="n">
+      <c r="BV22" t="n">
         <v>625.6</v>
       </c>
-      <c r="BN22" t="n">
+      <c r="BW22" t="n">
         <v>627.1</v>
       </c>
-      <c r="BO22" t="n">
+      <c r="BX22" t="n">
         <v>627.1</v>
       </c>
-      <c r="BP22" t="n">
+      <c r="BY22" t="n">
         <v>627.1</v>
       </c>
-      <c r="BQ22" t="n">
+      <c r="BZ22" t="n">
         <v>627.1</v>
       </c>
-      <c r="BR22" t="n">
+      <c r="CA22" t="n">
         <v>627.1</v>
       </c>
-      <c r="BS22" t="n">
+      <c r="CB22" t="n">
         <v>627.1</v>
       </c>
-      <c r="BT22" t="n">
-        <v>0.7297294372294372</v>
-      </c>
-      <c r="BU22" t="n">
-        <v>0.7453066378066378</v>
-      </c>
-      <c r="BV22" t="n">
-        <v>0.7939169327404623</v>
-      </c>
-      <c r="BW22" t="n">
-        <v>0.7409953454585975</v>
-      </c>
-      <c r="BX22" t="n">
-        <v>0.8478333716936659</v>
-      </c>
-      <c r="BY22" t="n">
-        <v>0.7555432236322329</v>
-      </c>
-      <c r="BZ22" t="n">
-        <v>0.7741129516410625</v>
-      </c>
-      <c r="CA22" t="n">
-        <v>0.8840634137543202</v>
-      </c>
-      <c r="CB22" t="n">
-        <v>0.8630272541444578</v>
+      <c r="CC22" t="inlineStr"/>
+      <c r="CD22" t="inlineStr"/>
+      <c r="CE22" t="inlineStr"/>
+      <c r="CF22" t="inlineStr"/>
+      <c r="CG22" t="inlineStr"/>
+      <c r="CH22" t="inlineStr"/>
+      <c r="CI22" t="inlineStr"/>
+      <c r="CJ22" t="inlineStr"/>
+      <c r="CK22" t="inlineStr"/>
+      <c r="CL22" t="n">
+        <v>501.6054999999999</v>
+      </c>
+      <c r="CM22" t="n">
+        <v>69.53700000000001</v>
       </c>
     </row>
     <row r="23">
@@ -6002,10 +6732,10 @@
         <v>1.785172850248165</v>
       </c>
       <c r="C23" t="n">
+        <v>2.04076264377075</v>
+      </c>
+      <c r="D23" t="n">
         <v>1.376494403223371</v>
-      </c>
-      <c r="D23" t="n">
-        <v>2.04076264377075</v>
       </c>
       <c r="E23" t="n">
         <v>1.785172850248165</v>
@@ -6014,224 +6744,239 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.01293709476863457</v>
-      </c>
-      <c r="H23" t="inlineStr"/>
+        <v>2.035701094799632</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.1692988637385316</v>
+      </c>
       <c r="I23" t="n">
-        <v>18.93914373269958</v>
+        <v>0.1674420559634382</v>
       </c>
       <c r="J23" t="n">
-        <v>66.45334094743703</v>
+        <v>0.1683073629436711</v>
       </c>
       <c r="K23" t="n">
-        <v>14.62921348389917</v>
+        <v>0.1636620394529371</v>
       </c>
       <c r="L23" t="n">
-        <v>20.67850601323225</v>
+        <v>0.1584223203306509</v>
       </c>
       <c r="M23" t="n">
-        <v>14.42584462668702</v>
+        <v>0.1616168308066954</v>
       </c>
       <c r="N23" t="n">
-        <v>16.12415014224317</v>
+        <v>0.2355039389546551</v>
       </c>
       <c r="O23" t="n">
-        <v>14.12012354019896</v>
+        <v>0.1575269400518694</v>
       </c>
       <c r="P23" t="n">
-        <v>15.42948540944298</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>14.79499683640473</v>
-      </c>
+        <v>0.1584165063170003</v>
+      </c>
+      <c r="Q23" t="inlineStr"/>
       <c r="R23" t="n">
-        <v>11.85421477060268</v>
+        <v>18.9385687226664</v>
       </c>
       <c r="S23" t="n">
-        <v>13.84740902810029</v>
+        <v>66.45283276010214</v>
       </c>
       <c r="T23" t="n">
-        <v>12.20306418983589</v>
+        <v>14.62946625460877</v>
       </c>
       <c r="U23" t="n">
-        <v>12.86295954650378</v>
+        <v>20.67746189122731</v>
       </c>
       <c r="V23" t="n">
-        <v>10.43556802478581</v>
+        <v>14.42543341499749</v>
       </c>
       <c r="W23" t="n">
-        <v>11.38775631081524</v>
+        <v>16.12463972669745</v>
       </c>
       <c r="X23" t="n">
-        <v>10.26799795096825</v>
+        <v>14.11966000597077</v>
       </c>
       <c r="Y23" t="n">
-        <v>10.22904858411567</v>
+        <v>15.42976290024882</v>
       </c>
       <c r="Z23" t="n">
-        <v>9.955936315472812</v>
+        <v>14.79483409131289</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.3234724930359671</v>
+        <v>11.85368803368808</v>
       </c>
       <c r="AB23" t="n">
-        <v>0.1748133555152521</v>
+        <v>13.84789423475072</v>
       </c>
       <c r="AC23" t="n">
-        <v>0.1263676421581718</v>
+        <v>12.20304684775163</v>
       </c>
       <c r="AD23" t="n">
-        <v>0.1094446776935674</v>
+        <v>12.86346237257009</v>
       </c>
       <c r="AE23" t="n">
-        <v>0.09899603395861498</v>
+        <v>10.43394070733635</v>
       </c>
       <c r="AF23" t="n">
-        <v>0.08232010336565178</v>
+        <v>11.38744225243894</v>
       </c>
       <c r="AG23" t="n">
-        <v>0.0621180409483503</v>
+        <v>10.26858423081114</v>
       </c>
       <c r="AH23" t="n">
-        <v>0.04828235115049821</v>
+        <v>10.22821663469815</v>
       </c>
       <c r="AI23" t="n">
-        <v>0.03977108891367688</v>
+        <v>9.954910504765714</v>
       </c>
       <c r="AJ23" t="n">
-        <v>18.5473866793028</v>
+        <v>0.3233394826689614</v>
       </c>
       <c r="AK23" t="n">
-        <v>14.29931589068234</v>
+        <v>0.1756334400481807</v>
       </c>
       <c r="AL23" t="n">
-        <v>13.02795678127375</v>
+        <v>0.1255262606200916</v>
       </c>
       <c r="AM23" t="n">
+        <v>0.1087960428846951</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>0.09875008327777968</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0.08181493879803563</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>0.06295361701075516</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0.04751454071068528</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>0.04089460136806118</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>18.54607250236981</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>14.29888286950381</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>13.02797197127053</v>
+      </c>
+      <c r="AV23" t="n">
         <v>13.13890801959464</v>
       </c>
-      <c r="AN23" t="n">
-        <v>13.76751863788258</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>13.52038380355709</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>12.17974238175914</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>11.5489288663371</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>11.02277425617669</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>13.81846867613204</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>10.1155165314758</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>9.480636605926389</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>10.01074441246546</v>
-      </c>
       <c r="AW23" t="n">
-        <v>9.847176930570438</v>
+        <v>13.76712884297039</v>
       </c>
       <c r="AX23" t="n">
-        <v>9.793404209827651</v>
+        <v>13.52097341559634</v>
       </c>
       <c r="AY23" t="n">
-        <v>9.487563639401532</v>
+        <v>12.17943014611975</v>
       </c>
       <c r="AZ23" t="n">
-        <v>9.173433288077199</v>
+        <v>11.54834023162043</v>
       </c>
       <c r="BA23" t="n">
-        <v>9.10876750967206</v>
+        <v>11.0240125945234</v>
       </c>
       <c r="BB23" t="n">
-        <v>56.0962284124812</v>
+        <v>13.81781150315932</v>
       </c>
       <c r="BC23" t="n">
+        <v>10.11575075914055</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>9.480437476026205</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>10.01106560130759</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>9.846933853529711</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>9.794090807055145</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>9.487808174039378</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>9.174254293516462</v>
+      </c>
+      <c r="BJ23" t="n">
+        <v>9.108578894299825</v>
+      </c>
+      <c r="BK23" t="n">
+        <v>56.09622841248121</v>
+      </c>
+      <c r="BL23" t="n">
         <v>43.44215755037472</v>
       </c>
-      <c r="BD23" t="n">
+      <c r="BM23" t="n">
         <v>40.08530377766107</v>
       </c>
-      <c r="BE23" t="n">
+      <c r="BN23" t="n">
         <v>38.20856889288194</v>
       </c>
-      <c r="BF23" t="n">
+      <c r="BO23" t="n">
         <v>37.81572354680551</v>
       </c>
-      <c r="BG23" t="n">
+      <c r="BP23" t="n">
         <v>37.75750186874684</v>
       </c>
-      <c r="BH23" t="n">
+      <c r="BQ23" t="n">
         <v>37.29060838447411</v>
       </c>
-      <c r="BI23" t="n">
+      <c r="BR23" t="n">
         <v>36.37852894800795</v>
       </c>
-      <c r="BJ23" t="n">
+      <c r="BS23" t="n">
         <v>36.37852894800795</v>
       </c>
-      <c r="BK23" t="n">
+      <c r="BT23" t="n">
         <v>30.37359483429472</v>
       </c>
-      <c r="BL23" t="n">
+      <c r="BU23" t="n">
         <v>25.79774571954934</v>
       </c>
-      <c r="BM23" t="n">
+      <c r="BV23" t="n">
         <v>22.66553144732048</v>
       </c>
-      <c r="BN23" t="n">
+      <c r="BW23" t="n">
         <v>21.12593816042011</v>
       </c>
-      <c r="BO23" t="n">
+      <c r="BX23" t="n">
         <v>21.12593816042011</v>
       </c>
-      <c r="BP23" t="n">
+      <c r="BY23" t="n">
         <v>21.12593816042011</v>
       </c>
-      <c r="BQ23" t="n">
+      <c r="BZ23" t="n">
         <v>21.12593816042011</v>
       </c>
-      <c r="BR23" t="n">
+      <c r="CA23" t="n">
         <v>21.12593816042011</v>
       </c>
-      <c r="BS23" t="n">
+      <c r="CB23" t="n">
         <v>21.12593816042011</v>
       </c>
-      <c r="BT23" t="n">
-        <v>0.2354504092043576</v>
-      </c>
-      <c r="BU23" t="n">
-        <v>0.2776790082959274</v>
-      </c>
-      <c r="BV23" t="n">
-        <v>0.1427989966158346</v>
-      </c>
-      <c r="BW23" t="n">
-        <v>0.211505198802261</v>
-      </c>
-      <c r="BX23" t="n">
-        <v>0.1261350476978781</v>
-      </c>
-      <c r="BY23" t="n">
-        <v>0.2530215413691934</v>
-      </c>
-      <c r="BZ23" t="n">
-        <v>0.2940453291972203</v>
-      </c>
-      <c r="CA23" t="n">
-        <v>0.08633835528014679</v>
-      </c>
-      <c r="CB23" t="n">
-        <v>0.1023604617372482</v>
+      <c r="CC23" t="inlineStr"/>
+      <c r="CD23" t="inlineStr"/>
+      <c r="CE23" t="inlineStr"/>
+      <c r="CF23" t="inlineStr"/>
+      <c r="CG23" t="inlineStr"/>
+      <c r="CH23" t="inlineStr"/>
+      <c r="CI23" t="inlineStr"/>
+      <c r="CJ23" t="inlineStr"/>
+      <c r="CK23" t="inlineStr"/>
+      <c r="CL23" t="n">
+        <v>10.22821663469815</v>
+      </c>
+      <c r="CM23" t="n">
+        <v>9.954910504765714</v>
       </c>
     </row>
   </sheetData>
